--- a/tmp/mock_incident_table_v3.xlsx
+++ b/tmp/mock_incident_table_v3.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="250">
   <si>
     <t>事件ID</t>
   </si>
@@ -215,9 +215,6 @@
     <t>检测到海莲花APT攻击攻击活动—端口扫描</t>
   </si>
   <si>
-    <t>192.168.76.20</t>
-  </si>
-  <si>
     <t>海莲花APT攻击</t>
   </si>
   <si>
@@ -371,274 +368,274 @@
     <t>检测到勒索攻击攻击活动—WebShell上传</t>
   </si>
   <si>
+    <t>WebShell上传</t>
+  </si>
+  <si>
+    <t>2026-06-24 00:00:00</t>
+  </si>
+  <si>
+    <t>2026-06-26 00:00:00</t>
+  </si>
+  <si>
+    <t>5.188.206.78</t>
+  </si>
+  <si>
+    <t>STA (B003EE),EDR (343300000000000007)</t>
+  </si>
+  <si>
+    <t>5.188.206.78（恶意）</t>
+  </si>
+  <si>
+    <t>ransom-bot.biz（恶意）</t>
+  </si>
+  <si>
+    <t>2026-06-23 22:00:00</t>
+  </si>
+  <si>
+    <t>incident-373a8fbb-9108-49cd-8c81-4e8776da5b6a</t>
+  </si>
+  <si>
+    <t>检测到银狐攻击攻击活动—DNS隧道</t>
+  </si>
+  <si>
+    <t>异常行为事件</t>
+  </si>
+  <si>
+    <t>2026-06-03 00:00:00</t>
+  </si>
+  <si>
+    <t>94.102.61.23</t>
+  </si>
+  <si>
+    <t>STA (B003EF),EDR (343300000000000008)</t>
+  </si>
+  <si>
+    <t>94.102.61.23（恶意）</t>
+  </si>
+  <si>
+    <t>2026-06-02 22:00:00</t>
+  </si>
+  <si>
+    <t>incident-08cddcf6-87ec-4051-91a1-1af581e6e57e</t>
+  </si>
+  <si>
+    <t>检测到海莲花APT攻击攻击活动—远程代码执行</t>
+  </si>
+  <si>
+    <t>远程代码执行</t>
+  </si>
+  <si>
+    <t>2026-06-06 00:00:00</t>
+  </si>
+  <si>
+    <t>2026-06-08 00:00:00</t>
+  </si>
+  <si>
+    <t>185.153.196.30</t>
+  </si>
+  <si>
+    <t>STA (B003F0),EDR (343300000000000009)</t>
+  </si>
+  <si>
+    <t>185.153.196.30（恶意）</t>
+  </si>
+  <si>
+    <t>2026-06-05 22:00:00</t>
+  </si>
+  <si>
+    <t>incident-c608fb20-d8e3-474b-b827-6b17c3cfc628</t>
+  </si>
+  <si>
+    <t>检测到响尾蛇APT攻击攻击活动—蠕虫传播</t>
+  </si>
+  <si>
+    <t>蠕虫传播</t>
+  </si>
+  <si>
+    <t>2026-06-01 00:00:00</t>
+  </si>
+  <si>
+    <t>146.185.239.120</t>
+  </si>
+  <si>
+    <t>STA (B003F1),EDR (343300000000000010)</t>
+  </si>
+  <si>
+    <t>146.185.239.120（恶意）</t>
+  </si>
+  <si>
+    <t>ddos-agent.net（恶意）</t>
+  </si>
+  <si>
+    <t>2026-05-31 22:00:00</t>
+  </si>
+  <si>
+    <t>incident-db2b4387-6cc5-49c0-90ce-5babab227c1b</t>
+  </si>
+  <si>
+    <t>检测到cobaltstrike远控攻击活动—CobaltStrike</t>
+  </si>
+  <si>
+    <t>10.245.224.255</t>
+  </si>
+  <si>
+    <t>cobaltstrike远控</t>
+  </si>
+  <si>
+    <t>渗透攻击事件</t>
+  </si>
+  <si>
+    <t>CobaltStrike</t>
+  </si>
+  <si>
+    <t>195.123.237.91</t>
+  </si>
+  <si>
+    <t>STA (B003F2),EDR (343300000000000011)</t>
+  </si>
+  <si>
+    <t>195.123.237.91（恶意）</t>
+  </si>
+  <si>
+    <t>incident-4d1c559a-2cdb-4ad9-95de-752d013f9501</t>
+  </si>
+  <si>
+    <t>检测到摩诃草APT攻击活动—DNS隧道</t>
+  </si>
+  <si>
+    <t>摩诃草APT</t>
+  </si>
+  <si>
+    <t>45.155.205.99</t>
+  </si>
+  <si>
+    <t>STA (B003F3),EDR (343300000000000012)</t>
+  </si>
+  <si>
+    <t>45.155.205.99（恶意）</t>
+  </si>
+  <si>
+    <t>已处置</t>
+  </si>
+  <si>
+    <t>incident-63d36b46-77cd-400f-be38-b920e711ce7d</t>
+  </si>
+  <si>
+    <t>检测到银狐病毒活动—病毒木马行为</t>
+  </si>
+  <si>
     <t>192.168.100.200</t>
   </si>
   <si>
-    <t>WebShell上传</t>
-  </si>
-  <si>
-    <t>2026-06-24 00:00:00</t>
-  </si>
-  <si>
-    <t>2026-06-26 00:00:00</t>
-  </si>
-  <si>
-    <t>5.188.206.78</t>
-  </si>
-  <si>
-    <t>STA (B003EE),EDR (343300000000000007)</t>
-  </si>
-  <si>
-    <t>5.188.206.78（恶意）</t>
-  </si>
-  <si>
-    <t>ransom-bot.biz（恶意）</t>
-  </si>
-  <si>
-    <t>2026-06-23 22:00:00</t>
-  </si>
-  <si>
-    <t>incident-373a8fbb-9108-49cd-8c81-4e8776da5b6a</t>
-  </si>
-  <si>
-    <t>检测到银狐攻击攻击活动—DNS隧道</t>
+    <t>病毒木马活动</t>
+  </si>
+  <si>
+    <t>银狐病毒</t>
+  </si>
+  <si>
+    <t>EDR (343300000000000100),STA (A07D0)</t>
+  </si>
+  <si>
+    <t>2026-06-18 23:00:00</t>
+  </si>
+  <si>
+    <t>incident-c7df0a06-bb71-46ee-8628-e29f645a93d7</t>
+  </si>
+  <si>
+    <t>检测到勒索病毒活动—WebShell上传</t>
   </si>
   <si>
     <t>172.17.75.124</t>
   </si>
   <si>
-    <t>异常行为事件</t>
-  </si>
-  <si>
-    <t>2026-06-03 00:00:00</t>
-  </si>
-  <si>
-    <t>94.102.61.23</t>
-  </si>
-  <si>
-    <t>STA (B003EF),EDR (343300000000000008)</t>
-  </si>
-  <si>
-    <t>94.102.61.23（恶意）</t>
-  </si>
-  <si>
-    <t>2026-06-02 22:00:00</t>
-  </si>
-  <si>
-    <t>incident-08cddcf6-87ec-4051-91a1-1af581e6e57e</t>
-  </si>
-  <si>
-    <t>检测到海莲花APT攻击攻击活动—远程代码执行</t>
+    <t>勒索病毒</t>
+  </si>
+  <si>
+    <t>EDR (343300000000000101),STA (A07D1)</t>
+  </si>
+  <si>
+    <t>updater.dll（恶意）</t>
+  </si>
+  <si>
+    <t>2026-06-05 23:00:00</t>
+  </si>
+  <si>
+    <t>incident-6070271d-a3e1-4801-8c67-6f895ecbf435</t>
+  </si>
+  <si>
+    <t>检测到挖矿病毒活动—数据窃取</t>
   </si>
   <si>
     <t>168.196.23.21</t>
   </si>
   <si>
-    <t>远程代码执行</t>
-  </si>
-  <si>
-    <t>2026-06-06 00:00:00</t>
-  </si>
-  <si>
-    <t>2026-06-08 00:00:00</t>
-  </si>
-  <si>
-    <t>185.153.196.30</t>
-  </si>
-  <si>
-    <t>STA (B003F0),EDR (343300000000000009)</t>
-  </si>
-  <si>
-    <t>185.153.196.30（恶意）</t>
-  </si>
-  <si>
-    <t>2026-06-05 22:00:00</t>
-  </si>
-  <si>
-    <t>incident-c608fb20-d8e3-474b-b827-6b17c3cfc628</t>
-  </si>
-  <si>
-    <t>检测到响尾蛇APT攻击攻击活动—蠕虫传播</t>
+    <t>挖矿病毒</t>
+  </si>
+  <si>
+    <t>数据窃取</t>
+  </si>
+  <si>
+    <t>EDR (343300000000000102),STA (A07D2)</t>
+  </si>
+  <si>
+    <t>system32.dll（恶意）</t>
+  </si>
+  <si>
+    <t>incident-394abd11-137d-431b-8a49-52c69b4dce5b</t>
+  </si>
+  <si>
+    <t>检测到后门木马活动—文件上传漏洞</t>
   </si>
   <si>
     <t>192.168.24.241</t>
   </si>
   <si>
-    <t>蠕虫传播</t>
-  </si>
-  <si>
-    <t>2026-06-01 00:00:00</t>
-  </si>
-  <si>
-    <t>146.185.239.120</t>
-  </si>
-  <si>
-    <t>STA (B003F1),EDR (343300000000000010)</t>
-  </si>
-  <si>
-    <t>146.185.239.120（恶意）</t>
-  </si>
-  <si>
-    <t>ddos-agent.net（恶意）</t>
-  </si>
-  <si>
-    <t>2026-05-31 22:00:00</t>
-  </si>
-  <si>
-    <t>incident-db2b4387-6cc5-49c0-90ce-5babab227c1b</t>
-  </si>
-  <si>
-    <t>检测到cobaltstrike远控攻击活动—CobaltStrike</t>
-  </si>
-  <si>
-    <t>10.245.224.255</t>
-  </si>
-  <si>
-    <t>cobaltstrike远控</t>
-  </si>
-  <si>
-    <t>渗透攻击事件</t>
-  </si>
-  <si>
-    <t>CobaltStrike</t>
-  </si>
-  <si>
-    <t>195.123.237.91</t>
-  </si>
-  <si>
-    <t>STA (B003F2),EDR (343300000000000011)</t>
-  </si>
-  <si>
-    <t>195.123.237.91（恶意）</t>
-  </si>
-  <si>
-    <t>incident-4d1c559a-2cdb-4ad9-95de-752d013f9501</t>
-  </si>
-  <si>
-    <t>检测到摩诃草APT攻击活动—DNS隧道</t>
+    <t>后门木马</t>
+  </si>
+  <si>
+    <t>文件上传漏洞</t>
+  </si>
+  <si>
+    <t>2026-06-27 00:00:00</t>
+  </si>
+  <si>
+    <t>2026-06-28 00:00:00</t>
+  </si>
+  <si>
+    <t>EDR (343300000000000103),STA (A07D3)</t>
+  </si>
+  <si>
+    <t>winlogon.exe（恶意）</t>
+  </si>
+  <si>
+    <t>2026-06-26 23:00:00</t>
+  </si>
+  <si>
+    <t>incident-58f520ea-72d3-4486-8e3f-040755ed7750</t>
+  </si>
+  <si>
+    <t>检测到下载者木马活动—蠕虫传播</t>
+  </si>
+  <si>
+    <t>下载者木马</t>
+  </si>
+  <si>
+    <t>EDR (343300000000000104),STA (A07D4)</t>
+  </si>
+  <si>
+    <t>explorer.dll（恶意）</t>
+  </si>
+  <si>
+    <t>2026-06-02 23:00:00</t>
+  </si>
+  <si>
+    <t>incident-9acde1de-c665-49d3-8a14-a2fe7dd5af2a</t>
+  </si>
+  <si>
+    <t>检测到蠕虫病毒活动—CobaltStrike</t>
   </si>
   <si>
     <t>192.168.118.232</t>
-  </si>
-  <si>
-    <t>摩诃草APT</t>
-  </si>
-  <si>
-    <t>45.155.205.99</t>
-  </si>
-  <si>
-    <t>STA (B003F3),EDR (343300000000000012)</t>
-  </si>
-  <si>
-    <t>45.155.205.99（恶意）</t>
-  </si>
-  <si>
-    <t>已处置</t>
-  </si>
-  <si>
-    <t>incident-63d36b46-77cd-400f-be38-b920e711ce7d</t>
-  </si>
-  <si>
-    <t>检测到银狐病毒活动—病毒木马行为</t>
-  </si>
-  <si>
-    <t>病毒木马活动</t>
-  </si>
-  <si>
-    <t>银狐病毒</t>
-  </si>
-  <si>
-    <t>EDR (343300000000000100),STA (A07D0)</t>
-  </si>
-  <si>
-    <t>2026-06-18 23:00:00</t>
-  </si>
-  <si>
-    <t>incident-c7df0a06-bb71-46ee-8628-e29f645a93d7</t>
-  </si>
-  <si>
-    <t>检测到勒索病毒活动—WebShell上传</t>
-  </si>
-  <si>
-    <t>勒索病毒</t>
-  </si>
-  <si>
-    <t>EDR (343300000000000101),STA (A07D1)</t>
-  </si>
-  <si>
-    <t>updater.dll（恶意）</t>
-  </si>
-  <si>
-    <t>2026-06-05 23:00:00</t>
-  </si>
-  <si>
-    <t>incident-6070271d-a3e1-4801-8c67-6f895ecbf435</t>
-  </si>
-  <si>
-    <t>检测到挖矿病毒活动—数据窃取</t>
-  </si>
-  <si>
-    <t>挖矿病毒</t>
-  </si>
-  <si>
-    <t>数据窃取</t>
-  </si>
-  <si>
-    <t>EDR (343300000000000102),STA (A07D2)</t>
-  </si>
-  <si>
-    <t>system32.dll（恶意）</t>
-  </si>
-  <si>
-    <t>incident-394abd11-137d-431b-8a49-52c69b4dce5b</t>
-  </si>
-  <si>
-    <t>检测到后门木马活动—文件上传漏洞</t>
-  </si>
-  <si>
-    <t>后门木马</t>
-  </si>
-  <si>
-    <t>文件上传漏洞</t>
-  </si>
-  <si>
-    <t>2026-06-27 00:00:00</t>
-  </si>
-  <si>
-    <t>2026-06-28 00:00:00</t>
-  </si>
-  <si>
-    <t>EDR (343300000000000103),STA (A07D3)</t>
-  </si>
-  <si>
-    <t>winlogon.exe（恶意）</t>
-  </si>
-  <si>
-    <t>2026-06-26 23:00:00</t>
-  </si>
-  <si>
-    <t>incident-58f520ea-72d3-4486-8e3f-040755ed7750</t>
-  </si>
-  <si>
-    <t>检测到下载者木马活动—蠕虫传播</t>
-  </si>
-  <si>
-    <t>下载者木马</t>
-  </si>
-  <si>
-    <t>EDR (343300000000000104),STA (A07D4)</t>
-  </si>
-  <si>
-    <t>explorer.dll（恶意）</t>
-  </si>
-  <si>
-    <t>2026-06-02 23:00:00</t>
-  </si>
-  <si>
-    <t>incident-9acde1de-c665-49d3-8a14-a2fe7dd5af2a</t>
-  </si>
-  <si>
-    <t>检测到蠕虫病毒活动—CobaltStrike</t>
   </si>
   <si>
     <t>蠕虫病毒</t>
@@ -1734,6 +1731,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="38.6666666666667" customWidth="1"/>
+    <col min="3" max="3" width="18.1111111111111" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
     <col min="9" max="9" width="17.3333333333333" customWidth="1"/>
     <col min="19" max="19" width="15" customWidth="1"/>
@@ -1960,7 +1958,7 @@
         <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="D4" t="s">
         <v>26</v>
@@ -1969,28 +1967,28 @@
         <v>27</v>
       </c>
       <c r="F4" t="s">
+        <v>61</v>
+      </c>
+      <c r="G4" t="s">
         <v>62</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>63</v>
-      </c>
-      <c r="H4" t="s">
-        <v>64</v>
       </c>
       <c r="I4" t="s">
         <v>49</v>
       </c>
       <c r="J4" t="s">
+        <v>64</v>
+      </c>
+      <c r="K4" t="s">
         <v>65</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>66</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>67</v>
-      </c>
-      <c r="M4" t="s">
-        <v>68</v>
       </c>
       <c r="N4" t="s">
         <v>36</v>
@@ -2002,36 +2000,36 @@
         <v>26</v>
       </c>
       <c r="Q4" t="s">
+        <v>68</v>
+      </c>
+      <c r="R4" t="s">
         <v>69</v>
       </c>
-      <c r="R4" t="s">
+      <c r="S4" t="s">
         <v>70</v>
       </c>
-      <c r="S4" t="s">
+      <c r="T4" t="s">
+        <v>26</v>
+      </c>
+      <c r="U4" t="s">
         <v>71</v>
       </c>
-      <c r="T4" t="s">
-        <v>26</v>
-      </c>
-      <c r="U4" t="s">
+      <c r="V4" t="s">
         <v>72</v>
       </c>
-      <c r="V4" t="s">
+      <c r="W4" t="s">
         <v>73</v>
-      </c>
-      <c r="W4" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:23">
       <c r="A5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B5" t="s">
         <v>75</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>76</v>
-      </c>
-      <c r="C5" t="s">
-        <v>77</v>
       </c>
       <c r="D5" t="s">
         <v>26</v>
@@ -2040,28 +2038,28 @@
         <v>27</v>
       </c>
       <c r="F5" t="s">
+        <v>77</v>
+      </c>
+      <c r="G5" t="s">
         <v>78</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>80</v>
       </c>
       <c r="I5" t="s">
         <v>49</v>
       </c>
       <c r="J5" t="s">
+        <v>80</v>
+      </c>
+      <c r="K5" t="s">
         <v>81</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
         <v>82</v>
       </c>
-      <c r="L5" t="s">
+      <c r="M5" t="s">
         <v>83</v>
-      </c>
-      <c r="M5" t="s">
-        <v>84</v>
       </c>
       <c r="N5" t="s">
         <v>36</v>
@@ -2073,36 +2071,36 @@
         <v>26</v>
       </c>
       <c r="Q5" t="s">
+        <v>84</v>
+      </c>
+      <c r="R5" t="s">
         <v>85</v>
       </c>
-      <c r="R5" t="s">
+      <c r="S5" t="s">
         <v>86</v>
       </c>
-      <c r="S5" t="s">
+      <c r="T5" t="s">
         <v>87</v>
       </c>
-      <c r="T5" t="s">
+      <c r="U5" t="s">
+        <v>26</v>
+      </c>
+      <c r="V5" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="U5" t="s">
-        <v>26</v>
-      </c>
-      <c r="V5" s="1" t="s">
+      <c r="W5" t="s">
         <v>89</v>
-      </c>
-      <c r="W5" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:23">
       <c r="A6" t="s">
+        <v>90</v>
+      </c>
+      <c r="B6" t="s">
         <v>91</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>92</v>
-      </c>
-      <c r="C6" t="s">
-        <v>93</v>
       </c>
       <c r="D6" t="s">
         <v>26</v>
@@ -2117,22 +2115,22 @@
         <v>29</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I6" t="s">
         <v>31</v>
       </c>
       <c r="J6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K6" t="s">
         <v>33</v>
       </c>
       <c r="L6" t="s">
+        <v>94</v>
+      </c>
+      <c r="M6" t="s">
         <v>95</v>
-      </c>
-      <c r="M6" t="s">
-        <v>96</v>
       </c>
       <c r="N6" t="s">
         <v>36</v>
@@ -2144,36 +2142,36 @@
         <v>26</v>
       </c>
       <c r="Q6" t="s">
+        <v>96</v>
+      </c>
+      <c r="R6" t="s">
         <v>97</v>
       </c>
-      <c r="R6" t="s">
+      <c r="S6" t="s">
         <v>98</v>
       </c>
-      <c r="S6" t="s">
+      <c r="T6" t="s">
+        <v>26</v>
+      </c>
+      <c r="U6" t="s">
+        <v>26</v>
+      </c>
+      <c r="V6" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="W6" t="s">
         <v>99</v>
-      </c>
-      <c r="T6" t="s">
-        <v>26</v>
-      </c>
-      <c r="U6" t="s">
-        <v>26</v>
-      </c>
-      <c r="V6" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="W6" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:23">
       <c r="A7" t="s">
+        <v>100</v>
+      </c>
+      <c r="B7" t="s">
         <v>101</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>102</v>
-      </c>
-      <c r="C7" t="s">
-        <v>103</v>
       </c>
       <c r="D7" t="s">
         <v>26</v>
@@ -2188,22 +2186,22 @@
         <v>47</v>
       </c>
       <c r="H7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I7" t="s">
         <v>49</v>
       </c>
       <c r="J7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K7" t="s">
         <v>51</v>
       </c>
       <c r="L7" t="s">
+        <v>104</v>
+      </c>
+      <c r="M7" t="s">
         <v>105</v>
-      </c>
-      <c r="M7" t="s">
-        <v>106</v>
       </c>
       <c r="N7" t="s">
         <v>36</v>
@@ -2215,36 +2213,36 @@
         <v>26</v>
       </c>
       <c r="Q7" t="s">
+        <v>106</v>
+      </c>
+      <c r="R7" t="s">
         <v>107</v>
       </c>
-      <c r="R7" t="s">
+      <c r="S7" t="s">
         <v>108</v>
       </c>
-      <c r="S7" t="s">
-        <v>109</v>
-      </c>
       <c r="T7" t="s">
         <v>26</v>
       </c>
       <c r="U7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="V7" t="s">
         <v>57</v>
       </c>
       <c r="W7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="8" spans="1:23">
       <c r="A8" t="s">
+        <v>110</v>
+      </c>
+      <c r="B8" t="s">
         <v>111</v>
       </c>
-      <c r="B8" t="s">
-        <v>112</v>
-      </c>
       <c r="C8" t="s">
-        <v>113</v>
+        <v>45</v>
       </c>
       <c r="D8" t="s">
         <v>26</v>
@@ -2256,25 +2254,25 @@
         <v>28</v>
       </c>
       <c r="G8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I8" t="s">
         <v>49</v>
       </c>
       <c r="J8" t="s">
+        <v>112</v>
+      </c>
+      <c r="K8" t="s">
+        <v>65</v>
+      </c>
+      <c r="L8" t="s">
+        <v>113</v>
+      </c>
+      <c r="M8" t="s">
         <v>114</v>
-      </c>
-      <c r="K8" t="s">
-        <v>66</v>
-      </c>
-      <c r="L8" t="s">
-        <v>115</v>
-      </c>
-      <c r="M8" t="s">
-        <v>116</v>
       </c>
       <c r="N8" t="s">
         <v>36</v>
@@ -2286,36 +2284,36 @@
         <v>26</v>
       </c>
       <c r="Q8" t="s">
+        <v>115</v>
+      </c>
+      <c r="R8" t="s">
+        <v>116</v>
+      </c>
+      <c r="S8" t="s">
         <v>117</v>
       </c>
-      <c r="R8" t="s">
+      <c r="T8" t="s">
         <v>118</v>
       </c>
-      <c r="S8" t="s">
+      <c r="U8" t="s">
+        <v>71</v>
+      </c>
+      <c r="V8" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="W8" t="s">
         <v>119</v>
-      </c>
-      <c r="T8" t="s">
-        <v>120</v>
-      </c>
-      <c r="U8" t="s">
-        <v>72</v>
-      </c>
-      <c r="V8" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="W8" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="9" spans="1:23">
       <c r="A9" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B9" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C9" t="s">
-        <v>124</v>
+        <v>45</v>
       </c>
       <c r="D9" t="s">
         <v>26</v>
@@ -2324,28 +2322,28 @@
         <v>27</v>
       </c>
       <c r="F9" t="s">
+        <v>77</v>
+      </c>
+      <c r="G9" t="s">
         <v>78</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="I9" t="s">
+        <v>122</v>
+      </c>
+      <c r="J9" t="s">
         <v>80</v>
       </c>
-      <c r="I9" t="s">
-        <v>125</v>
-      </c>
-      <c r="J9" t="s">
+      <c r="K9" t="s">
         <v>81</v>
       </c>
-      <c r="K9" t="s">
-        <v>82</v>
-      </c>
       <c r="L9" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="M9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="N9" t="s">
         <v>36</v>
@@ -2357,36 +2355,36 @@
         <v>26</v>
       </c>
       <c r="Q9" t="s">
+        <v>124</v>
+      </c>
+      <c r="R9" t="s">
+        <v>125</v>
+      </c>
+      <c r="S9" t="s">
+        <v>126</v>
+      </c>
+      <c r="T9" t="s">
+        <v>26</v>
+      </c>
+      <c r="U9" t="s">
+        <v>71</v>
+      </c>
+      <c r="V9" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="W9" t="s">
         <v>127</v>
-      </c>
-      <c r="R9" t="s">
-        <v>128</v>
-      </c>
-      <c r="S9" t="s">
-        <v>129</v>
-      </c>
-      <c r="T9" t="s">
-        <v>26</v>
-      </c>
-      <c r="U9" t="s">
-        <v>72</v>
-      </c>
-      <c r="V9" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="W9" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="10" ht="8" customHeight="1" spans="1:23">
       <c r="A10" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B10" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C10" t="s">
-        <v>133</v>
+        <v>45</v>
       </c>
       <c r="D10" t="s">
         <v>26</v>
@@ -2401,22 +2399,22 @@
         <v>29</v>
       </c>
       <c r="H10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I10" t="s">
         <v>31</v>
       </c>
       <c r="J10" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="K10" t="s">
         <v>33</v>
       </c>
       <c r="L10" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="M10" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="N10" t="s">
         <v>36</v>
@@ -2428,13 +2426,13 @@
         <v>26</v>
       </c>
       <c r="Q10" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="R10" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="S10" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="T10" t="s">
         <v>26</v>
@@ -2446,18 +2444,18 @@
         <v>41</v>
       </c>
       <c r="W10" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11" ht="8" customHeight="1" spans="1:23">
       <c r="A11" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B11" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C11" t="s">
-        <v>143</v>
+        <v>45</v>
       </c>
       <c r="D11" t="s">
         <v>26</v>
@@ -2472,22 +2470,22 @@
         <v>47</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I11" t="s">
         <v>49</v>
       </c>
       <c r="J11" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="K11" t="s">
         <v>51</v>
       </c>
       <c r="L11" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="M11" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="N11" t="s">
         <v>36</v>
@@ -2499,36 +2497,36 @@
         <v>26</v>
       </c>
       <c r="Q11" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="R11" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="S11" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="T11" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="U11" t="s">
         <v>26</v>
       </c>
       <c r="V11" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="W11" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
     </row>
     <row r="12" ht="8" customHeight="1" spans="1:23">
       <c r="A12" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="B12" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="C12" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="D12" t="s">
         <v>26</v>
@@ -2537,28 +2535,28 @@
         <v>27</v>
       </c>
       <c r="F12" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="G12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H12" t="s">
         <v>48</v>
       </c>
       <c r="I12" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="J12" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="K12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L12" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="M12" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="N12" t="s">
         <v>36</v>
@@ -2570,13 +2568,13 @@
         <v>26</v>
       </c>
       <c r="Q12" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="R12" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="S12" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="T12" t="s">
         <v>26</v>
@@ -2585,21 +2583,21 @@
         <v>26</v>
       </c>
       <c r="V12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="W12" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13" ht="8" customHeight="1" spans="1:23">
       <c r="A13" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="B13" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="C13" t="s">
-        <v>162</v>
+        <v>45</v>
       </c>
       <c r="D13" t="s">
         <v>26</v>
@@ -2608,28 +2606,28 @@
         <v>27</v>
       </c>
       <c r="F13" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="G13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I13" t="s">
         <v>49</v>
       </c>
       <c r="J13" t="s">
+        <v>80</v>
+      </c>
+      <c r="K13" t="s">
         <v>81</v>
       </c>
-      <c r="K13" t="s">
-        <v>82</v>
-      </c>
       <c r="L13" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="M13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="N13" t="s">
         <v>36</v>
@@ -2641,13 +2639,13 @@
         <v>26</v>
       </c>
       <c r="Q13" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="R13" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="S13" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="T13" t="s">
         <v>26</v>
@@ -2656,30 +2654,30 @@
         <v>26</v>
       </c>
       <c r="V13" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="W13" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14" ht="8" customHeight="1" spans="1:23">
       <c r="A14" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="B14" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="C14" t="s">
-        <v>113</v>
+        <v>164</v>
       </c>
       <c r="D14" t="s">
         <v>26</v>
       </c>
       <c r="E14" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="F14" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="G14" t="s">
         <v>47</v>
@@ -2691,16 +2689,16 @@
         <v>49</v>
       </c>
       <c r="J14" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L14" t="s">
         <v>52</v>
       </c>
       <c r="M14" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N14" t="s">
         <v>36</v>
@@ -2712,62 +2710,62 @@
         <v>26</v>
       </c>
       <c r="Q14" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="R14" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="S14"/>
       <c r="T14"/>
       <c r="U14" t="s">
+        <v>71</v>
+      </c>
+      <c r="V14" t="s">
         <v>72</v>
       </c>
-      <c r="V14" t="s">
-        <v>73</v>
-      </c>
       <c r="W14" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
     </row>
     <row r="15" ht="8" customHeight="1" spans="1:23">
       <c r="A15" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="B15" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="C15" t="s">
-        <v>124</v>
+        <v>171</v>
       </c>
       <c r="D15" t="s">
         <v>26</v>
       </c>
       <c r="E15" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="F15" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="G15" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I15" t="s">
         <v>49</v>
       </c>
       <c r="J15" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="K15" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L15" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="M15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="N15" t="s">
         <v>36</v>
@@ -2782,54 +2780,54 @@
         <v>26</v>
       </c>
       <c r="R15" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="S15" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="T15" t="s">
         <v>26</v>
       </c>
       <c r="U15" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="V15" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="W15" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
     </row>
     <row r="16" ht="8" customHeight="1" spans="1:23">
       <c r="A16" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="B16" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C16" t="s">
-        <v>133</v>
+        <v>178</v>
       </c>
       <c r="D16" t="s">
         <v>26</v>
       </c>
       <c r="E16" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="F16" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="G16" t="s">
+        <v>78</v>
+      </c>
+      <c r="H16" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>80</v>
       </c>
       <c r="I16" t="s">
         <v>49</v>
       </c>
       <c r="J16" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="K16" t="s">
         <v>33</v>
@@ -2838,7 +2836,7 @@
         <v>52</v>
       </c>
       <c r="M16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N16" t="s">
         <v>36</v>
@@ -2853,7 +2851,7 @@
         <v>26</v>
       </c>
       <c r="R16" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="S16" t="s">
         <v>26</v>
@@ -2862,33 +2860,33 @@
         <v>26</v>
       </c>
       <c r="U16" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="V16" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="W16" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
     </row>
     <row r="17" ht="8" customHeight="1" spans="1:23">
       <c r="A17" t="s">
+        <v>183</v>
+      </c>
+      <c r="B17" t="s">
+        <v>184</v>
+      </c>
+      <c r="C17" t="s">
+        <v>185</v>
+      </c>
+      <c r="D17" t="s">
+        <v>26</v>
+      </c>
+      <c r="E17" t="s">
+        <v>165</v>
+      </c>
+      <c r="F17" t="s">
         <v>186</v>
-      </c>
-      <c r="B17" t="s">
-        <v>187</v>
-      </c>
-      <c r="C17" t="s">
-        <v>143</v>
-      </c>
-      <c r="D17" t="s">
-        <v>26</v>
-      </c>
-      <c r="E17" t="s">
-        <v>170</v>
-      </c>
-      <c r="F17" t="s">
-        <v>188</v>
       </c>
       <c r="G17" t="s">
         <v>29</v>
@@ -2900,16 +2898,16 @@
         <v>31</v>
       </c>
       <c r="J17" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="K17" t="s">
         <v>51</v>
       </c>
       <c r="L17" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="M17" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="N17" t="s">
         <v>36</v>
@@ -2921,10 +2919,10 @@
         <v>26</v>
       </c>
       <c r="Q17" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="R17" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="S17" t="s">
         <v>26</v>
@@ -2933,54 +2931,54 @@
         <v>26</v>
       </c>
       <c r="U17" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="V17" t="s">
         <v>57</v>
       </c>
       <c r="W17" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="18" ht="8" customHeight="1" spans="1:23">
       <c r="A18" t="s">
+        <v>193</v>
+      </c>
+      <c r="B18" t="s">
+        <v>194</v>
+      </c>
+      <c r="C18" t="s">
+        <v>148</v>
+      </c>
+      <c r="D18" t="s">
+        <v>26</v>
+      </c>
+      <c r="E18" t="s">
+        <v>165</v>
+      </c>
+      <c r="F18" t="s">
         <v>195</v>
-      </c>
-      <c r="B18" t="s">
-        <v>196</v>
-      </c>
-      <c r="C18" t="s">
-        <v>153</v>
-      </c>
-      <c r="D18" t="s">
-        <v>26</v>
-      </c>
-      <c r="E18" t="s">
-        <v>170</v>
-      </c>
-      <c r="F18" t="s">
-        <v>197</v>
       </c>
       <c r="G18" t="s">
         <v>47</v>
       </c>
       <c r="H18" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I18" t="s">
         <v>49</v>
       </c>
       <c r="J18" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="K18" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L18" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="M18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="N18" t="s">
         <v>36</v>
@@ -2995,63 +2993,63 @@
         <v>26</v>
       </c>
       <c r="R18" t="s">
+        <v>196</v>
+      </c>
+      <c r="S18" t="s">
+        <v>154</v>
+      </c>
+      <c r="T18" t="s">
+        <v>87</v>
+      </c>
+      <c r="U18" t="s">
+        <v>197</v>
+      </c>
+      <c r="V18" t="s">
+        <v>72</v>
+      </c>
+      <c r="W18" t="s">
         <v>198</v>
-      </c>
-      <c r="S18" t="s">
-        <v>159</v>
-      </c>
-      <c r="T18" t="s">
-        <v>88</v>
-      </c>
-      <c r="U18" t="s">
-        <v>199</v>
-      </c>
-      <c r="V18" t="s">
-        <v>73</v>
-      </c>
-      <c r="W18" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="19" ht="8" customHeight="1" spans="1:23">
       <c r="A19" t="s">
+        <v>199</v>
+      </c>
+      <c r="B19" t="s">
+        <v>200</v>
+      </c>
+      <c r="C19" t="s">
         <v>201</v>
       </c>
-      <c r="B19" t="s">
+      <c r="D19" t="s">
+        <v>26</v>
+      </c>
+      <c r="E19" t="s">
+        <v>165</v>
+      </c>
+      <c r="F19" t="s">
         <v>202</v>
       </c>
-      <c r="C19" t="s">
-        <v>162</v>
-      </c>
-      <c r="D19" t="s">
-        <v>26</v>
-      </c>
-      <c r="E19" t="s">
-        <v>170</v>
-      </c>
-      <c r="F19" t="s">
-        <v>203</v>
-      </c>
       <c r="G19" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H19" t="s">
         <v>30</v>
       </c>
       <c r="I19" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="J19" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="K19" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L19" t="s">
         <v>35</v>
       </c>
       <c r="M19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="N19" t="s">
         <v>36</v>
@@ -3066,61 +3064,61 @@
         <v>26</v>
       </c>
       <c r="R19" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="S19" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="T19"/>
       <c r="U19" t="s">
+        <v>205</v>
+      </c>
+      <c r="V19" t="s">
+        <v>161</v>
+      </c>
+      <c r="W19" t="s">
         <v>206</v>
-      </c>
-      <c r="V19" t="s">
-        <v>167</v>
-      </c>
-      <c r="W19" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="20" ht="8" customHeight="1" spans="1:23">
       <c r="A20" t="s">
+        <v>207</v>
+      </c>
+      <c r="B20" t="s">
         <v>208</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>209</v>
       </c>
-      <c r="C20" t="s">
-        <v>210</v>
-      </c>
       <c r="D20" t="s">
         <v>26</v>
       </c>
       <c r="E20" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="F20" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="G20" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H20" t="s">
         <v>48</v>
       </c>
       <c r="I20" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="J20" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="K20" t="s">
         <v>33</v>
       </c>
       <c r="L20" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="M20" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="N20" t="s">
         <v>36</v>
@@ -3132,66 +3130,66 @@
         <v>26</v>
       </c>
       <c r="Q20" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="R20" t="s">
+        <v>210</v>
+      </c>
+      <c r="S20" t="s">
+        <v>26</v>
+      </c>
+      <c r="T20" t="s">
+        <v>26</v>
+      </c>
+      <c r="U20" t="s">
         <v>211</v>
-      </c>
-      <c r="S20" t="s">
-        <v>26</v>
-      </c>
-      <c r="T20" t="s">
-        <v>26</v>
-      </c>
-      <c r="U20" t="s">
-        <v>212</v>
       </c>
       <c r="V20" t="s">
         <v>41</v>
       </c>
       <c r="W20" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
     </row>
     <row r="21" ht="8" customHeight="1" spans="1:23">
       <c r="A21" t="s">
+        <v>212</v>
+      </c>
+      <c r="B21" t="s">
         <v>213</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>214</v>
       </c>
-      <c r="C21" t="s">
-        <v>215</v>
-      </c>
       <c r="D21" t="s">
         <v>26</v>
       </c>
       <c r="E21" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="F21" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="G21" t="s">
         <v>29</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I21" t="s">
         <v>31</v>
       </c>
       <c r="J21" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K21" t="s">
         <v>51</v>
       </c>
       <c r="L21" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="M21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="N21" t="s">
         <v>36</v>
@@ -3206,42 +3204,42 @@
         <v>26</v>
       </c>
       <c r="R21" t="s">
+        <v>216</v>
+      </c>
+      <c r="S21" t="s">
+        <v>26</v>
+      </c>
+      <c r="T21" t="s">
+        <v>26</v>
+      </c>
+      <c r="U21" t="s">
         <v>217</v>
-      </c>
-      <c r="S21" t="s">
-        <v>26</v>
-      </c>
-      <c r="T21" t="s">
-        <v>26</v>
-      </c>
-      <c r="U21" t="s">
-        <v>218</v>
       </c>
       <c r="V21" t="s">
         <v>57</v>
       </c>
       <c r="W21" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="22" ht="8" customHeight="1" spans="1:23">
       <c r="A22" t="s">
+        <v>219</v>
+      </c>
+      <c r="B22" t="s">
         <v>220</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
         <v>221</v>
       </c>
-      <c r="C22" t="s">
-        <v>222</v>
-      </c>
       <c r="D22" t="s">
         <v>26</v>
       </c>
       <c r="E22" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="F22" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="G22" t="s">
         <v>47</v>
@@ -3250,19 +3248,19 @@
         <v>30</v>
       </c>
       <c r="I22" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="J22" t="s">
+        <v>222</v>
+      </c>
+      <c r="K22" t="s">
+        <v>65</v>
+      </c>
+      <c r="L22" t="s">
+        <v>113</v>
+      </c>
+      <c r="M22" t="s">
         <v>223</v>
-      </c>
-      <c r="K22" t="s">
-        <v>66</v>
-      </c>
-      <c r="L22" t="s">
-        <v>115</v>
-      </c>
-      <c r="M22" t="s">
-        <v>224</v>
       </c>
       <c r="N22" t="s">
         <v>36</v>
@@ -3277,61 +3275,61 @@
         <v>26</v>
       </c>
       <c r="R22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="S22"/>
       <c r="T22" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="U22" t="s">
+        <v>225</v>
+      </c>
+      <c r="V22" t="s">
+        <v>72</v>
+      </c>
+      <c r="W22" t="s">
         <v>226</v>
-      </c>
-      <c r="V22" t="s">
-        <v>73</v>
-      </c>
-      <c r="W22" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="23" ht="8" customHeight="1" spans="1:23">
       <c r="A23" t="s">
+        <v>227</v>
+      </c>
+      <c r="B23" t="s">
         <v>228</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
         <v>229</v>
       </c>
-      <c r="C23" t="s">
-        <v>230</v>
-      </c>
       <c r="D23" t="s">
         <v>26</v>
       </c>
       <c r="E23" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="F23" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G23" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H23" t="s">
         <v>48</v>
       </c>
       <c r="I23" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="J23" t="s">
+        <v>230</v>
+      </c>
+      <c r="K23" t="s">
+        <v>81</v>
+      </c>
+      <c r="L23" t="s">
         <v>231</v>
       </c>
-      <c r="K23" t="s">
-        <v>82</v>
-      </c>
-      <c r="L23" t="s">
+      <c r="M23" t="s">
         <v>232</v>
-      </c>
-      <c r="M23" t="s">
-        <v>233</v>
       </c>
       <c r="N23" t="s">
         <v>36</v>
@@ -3346,63 +3344,63 @@
         <v>37</v>
       </c>
       <c r="R23" t="s">
+        <v>233</v>
+      </c>
+      <c r="S23" t="s">
+        <v>26</v>
+      </c>
+      <c r="T23" t="s">
+        <v>26</v>
+      </c>
+      <c r="U23" t="s">
         <v>234</v>
       </c>
-      <c r="S23" t="s">
-        <v>26</v>
-      </c>
-      <c r="T23" t="s">
-        <v>26</v>
-      </c>
-      <c r="U23" t="s">
+      <c r="V23" t="s">
+        <v>161</v>
+      </c>
+      <c r="W23" t="s">
         <v>235</v>
-      </c>
-      <c r="V23" t="s">
-        <v>167</v>
-      </c>
-      <c r="W23" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="24" ht="8" customHeight="1" spans="1:23">
       <c r="A24" t="s">
+        <v>236</v>
+      </c>
+      <c r="B24" t="s">
         <v>237</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
         <v>238</v>
       </c>
-      <c r="C24" t="s">
-        <v>239</v>
-      </c>
       <c r="D24" t="s">
         <v>26</v>
       </c>
       <c r="E24" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="F24" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="G24" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H24" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I24" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="J24" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="K24" t="s">
         <v>33</v>
       </c>
       <c r="L24" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M24" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="N24" t="s">
         <v>36</v>
@@ -3417,40 +3415,40 @@
         <v>26</v>
       </c>
       <c r="R24" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="S24" t="s">
         <v>26</v>
       </c>
       <c r="T24"/>
       <c r="U24" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="V24" t="s">
         <v>41</v>
       </c>
       <c r="W24" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="25" ht="8" customHeight="1" spans="1:23">
       <c r="A25" t="s">
+        <v>243</v>
+      </c>
+      <c r="B25" t="s">
         <v>244</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
         <v>245</v>
       </c>
-      <c r="C25" t="s">
-        <v>246</v>
-      </c>
       <c r="D25" t="s">
         <v>26</v>
       </c>
       <c r="E25" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="F25" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G25" t="s">
         <v>29</v>
@@ -3459,19 +3457,19 @@
         <v>30</v>
       </c>
       <c r="I25" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="J25" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="K25" t="s">
         <v>51</v>
       </c>
       <c r="L25" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="M25" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="N25" t="s">
         <v>36</v>
@@ -3486,22 +3484,22 @@
         <v>26</v>
       </c>
       <c r="R25" t="s">
+        <v>247</v>
+      </c>
+      <c r="S25" t="s">
+        <v>26</v>
+      </c>
+      <c r="T25" t="s">
+        <v>26</v>
+      </c>
+      <c r="U25" t="s">
         <v>248</v>
-      </c>
-      <c r="S25" t="s">
-        <v>26</v>
-      </c>
-      <c r="T25" t="s">
-        <v>26</v>
-      </c>
-      <c r="U25" t="s">
-        <v>249</v>
       </c>
       <c r="V25" t="s">
         <v>57</v>
       </c>
       <c r="W25" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="26" ht="8" customHeight="1"/>

--- a/tmp/mock_incident_table_v3.xlsx
+++ b/tmp/mock_incident_table_v3.xlsx
@@ -10,7 +10,7 @@
     <sheet name="事件表" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">事件表!$A$1:$W$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">事件表!$A$1:$W$25</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="226">
   <si>
     <t>事件ID</t>
   </si>
@@ -131,189 +131,192 @@
     <t>Web应用漏洞</t>
   </si>
   <si>
+    <t>成功</t>
+  </si>
+  <si>
+    <t>2026-06-15 00:00:00</t>
+  </si>
+  <si>
+    <t>2026-06-17 00:00:00</t>
+  </si>
+  <si>
+    <t>测试001</t>
+  </si>
+  <si>
+    <t>45.33.32.156</t>
+  </si>
+  <si>
+    <t>STA (B003E8),EDR (343300000000000001)</t>
+  </si>
+  <si>
+    <t>45.33.32.156（恶意）</t>
+  </si>
+  <si>
+    <t>evil-c2.xyz（恶意）</t>
+  </si>
+  <si>
+    <t>待处理</t>
+  </si>
+  <si>
+    <t>2026-06-14 22:00:00</t>
+  </si>
+  <si>
+    <t>incident-89635cc4-1b23-44ca-a765-19ccf893c446</t>
+  </si>
+  <si>
+    <t>检测到银狐攻击攻击活动—勒索软件活动</t>
+  </si>
+  <si>
+    <t>192.168.213.156</t>
+  </si>
+  <si>
+    <t>银狐攻击</t>
+  </si>
+  <si>
+    <t>高危</t>
+  </si>
+  <si>
+    <t>已处理</t>
+  </si>
+  <si>
+    <t>恶意程序事件</t>
+  </si>
+  <si>
+    <t>勒索软件活动</t>
+  </si>
+  <si>
+    <t>攻击</t>
+  </si>
+  <si>
+    <t>2026-06-19 00:00:00</t>
+  </si>
+  <si>
+    <t>2026-06-21 00:00:00</t>
+  </si>
+  <si>
+    <t>103.235.46.91</t>
+  </si>
+  <si>
+    <t>STA (B003E9),EDR (343300000000000002)</t>
+  </si>
+  <si>
+    <t>103.235.46.91（恶意）</t>
+  </si>
+  <si>
+    <t>已遏制</t>
+  </si>
+  <si>
+    <t>2026-06-18 22:00:00</t>
+  </si>
+  <si>
+    <t>incident-eaa7bbf6-fade-4c6f-9e52-dc13af32cea8</t>
+  </si>
+  <si>
+    <t>检测到海莲花APT攻击攻击活动—端口扫描</t>
+  </si>
+  <si>
+    <t>192.168.76.20</t>
+  </si>
+  <si>
+    <t>海莲花APT攻击</t>
+  </si>
+  <si>
+    <t>中危</t>
+  </si>
+  <si>
+    <t>处理中</t>
+  </si>
+  <si>
+    <t>端口扫描</t>
+  </si>
+  <si>
+    <t>2026-06-05 00:00:00</t>
+  </si>
+  <si>
+    <t>2026-06-07 00:00:00</t>
+  </si>
+  <si>
+    <t>185.220.101.34</t>
+  </si>
+  <si>
+    <t>STA (B003EA),EDR (343300000000000003)</t>
+  </si>
+  <si>
+    <t>185.220.101.34（恶意）</t>
+  </si>
+  <si>
+    <t>svchost.exe（恶意）</t>
+  </si>
+  <si>
+    <t>处置中</t>
+  </si>
+  <si>
+    <t>2026-06-04 22:00:00</t>
+  </si>
+  <si>
+    <t>incident-beb401e9-92e6-48b6-87a8-5afc3dbe02a2</t>
+  </si>
+  <si>
+    <t>检测到响尾蛇APT攻击攻击活动—DNS隧道</t>
+  </si>
+  <si>
+    <t>192.168.200.33</t>
+  </si>
+  <si>
+    <t>响尾蛇APT攻击</t>
+  </si>
+  <si>
+    <t>低危</t>
+  </si>
+  <si>
+    <t>处置完成</t>
+  </si>
+  <si>
+    <t>DNS隧道</t>
+  </si>
+  <si>
+    <t>未成功</t>
+  </si>
+  <si>
+    <t>2026-06-02 00:00:00</t>
+  </si>
+  <si>
+    <t>2026-06-04 00:00:00</t>
+  </si>
+  <si>
+    <t>198.54.117.210</t>
+  </si>
+  <si>
+    <t>STA (B003EB),EDR (343300000000000004)</t>
+  </si>
+  <si>
+    <t>198.54.117.210（恶意）</t>
+  </si>
+  <si>
+    <t>backdoor-gate.net（恶意）</t>
+  </si>
+  <si>
+    <t>已推送</t>
+  </si>
+  <si>
+    <t>2026-06-01 22:00:00</t>
+  </si>
+  <si>
+    <t>incident-b1e6ff99-b2fc-44d0-894c-5c954ffa927e</t>
+  </si>
+  <si>
+    <t>检测到cobaltstrike远控攻击活动—SQL注入漏洞</t>
+  </si>
+  <si>
+    <t>192.168.200.22</t>
+  </si>
+  <si>
+    <t>SQL注入漏洞</t>
+  </si>
+  <si>
     <t>失陷</t>
   </si>
   <si>
-    <t>2026-06-15 00:00:00</t>
-  </si>
-  <si>
-    <t>2026-06-17 00:00:00</t>
-  </si>
-  <si>
-    <t>测试001</t>
-  </si>
-  <si>
-    <t>45.33.32.156</t>
-  </si>
-  <si>
-    <t>STA (B003E8),EDR (343300000000000001)</t>
-  </si>
-  <si>
-    <t>45.33.32.156（恶意）</t>
-  </si>
-  <si>
-    <t>evil-c2.xyz（恶意）</t>
-  </si>
-  <si>
-    <t>待处理</t>
-  </si>
-  <si>
-    <t>2026-06-14 22:00:00</t>
-  </si>
-  <si>
-    <t>incident-89635cc4-1b23-44ca-a765-19ccf893c446</t>
-  </si>
-  <si>
-    <t>检测到银狐攻击攻击活动—勒索软件活动</t>
-  </si>
-  <si>
-    <t>192.168.213.156</t>
-  </si>
-  <si>
-    <t>银狐攻击</t>
-  </si>
-  <si>
-    <t>高危</t>
-  </si>
-  <si>
-    <t>已处理</t>
-  </si>
-  <si>
-    <t>恶意程序事件</t>
-  </si>
-  <si>
-    <t>勒索软件活动</t>
-  </si>
-  <si>
-    <t>攻击</t>
-  </si>
-  <si>
-    <t>2026-06-19 00:00:00</t>
-  </si>
-  <si>
-    <t>2026-06-21 00:00:00</t>
-  </si>
-  <si>
-    <t>103.235.46.91</t>
-  </si>
-  <si>
-    <t>STA (B003E9),EDR (343300000000000002)</t>
-  </si>
-  <si>
-    <t>103.235.46.91（恶意）</t>
-  </si>
-  <si>
-    <t>已遏制</t>
-  </si>
-  <si>
-    <t>2026-06-18 22:00:00</t>
-  </si>
-  <si>
-    <t>incident-eaa7bbf6-fade-4c6f-9e52-dc13af32cea8</t>
-  </si>
-  <si>
-    <t>检测到海莲花APT攻击攻击活动—端口扫描</t>
-  </si>
-  <si>
-    <t>海莲花APT攻击</t>
-  </si>
-  <si>
-    <t>中危</t>
-  </si>
-  <si>
-    <t>处理中</t>
-  </si>
-  <si>
-    <t>端口扫描</t>
-  </si>
-  <si>
-    <t>成功</t>
-  </si>
-  <si>
-    <t>2026-06-05 00:00:00</t>
-  </si>
-  <si>
-    <t>2026-06-07 00:00:00</t>
-  </si>
-  <si>
-    <t>185.220.101.34</t>
-  </si>
-  <si>
-    <t>STA (B003EA),EDR (343300000000000003)</t>
-  </si>
-  <si>
-    <t>185.220.101.34（恶意）</t>
-  </si>
-  <si>
-    <t>svchost.exe（恶意）</t>
-  </si>
-  <si>
-    <t>处置中</t>
-  </si>
-  <si>
-    <t>2026-06-04 22:00:00</t>
-  </si>
-  <si>
-    <t>incident-beb401e9-92e6-48b6-87a8-5afc3dbe02a2</t>
-  </si>
-  <si>
-    <t>检测到响尾蛇APT攻击攻击活动—DNS隧道</t>
-  </si>
-  <si>
-    <t>192.168.200.33</t>
-  </si>
-  <si>
-    <t>响尾蛇APT攻击</t>
-  </si>
-  <si>
-    <t>低危</t>
-  </si>
-  <si>
-    <t>处置完成</t>
-  </si>
-  <si>
-    <t>DNS隧道</t>
-  </si>
-  <si>
-    <t>未成功</t>
-  </si>
-  <si>
-    <t>2026-06-02 00:00:00</t>
-  </si>
-  <si>
-    <t>2026-06-04 00:00:00</t>
-  </si>
-  <si>
-    <t>198.54.117.210</t>
-  </si>
-  <si>
-    <t>STA (B003EB),EDR (343300000000000004)</t>
-  </si>
-  <si>
-    <t>198.54.117.210（恶意）</t>
-  </si>
-  <si>
-    <t>backdoor-gate.net（恶意）</t>
-  </si>
-  <si>
-    <t>已推送</t>
-  </si>
-  <si>
-    <t>2026-06-01 22:00:00</t>
-  </si>
-  <si>
-    <t>incident-ccb79f5b-0c52-45c8-8727-a49ee56da964</t>
-  </si>
-  <si>
-    <t>检测到cobaltstrike远控攻击活动—SQL注入漏洞</t>
-  </si>
-  <si>
-    <t>192.168.200.22</t>
-  </si>
-  <si>
-    <t>SQL注入漏洞</t>
-  </si>
-  <si>
     <t>2026-06-11 00:00:00</t>
   </si>
   <si>
@@ -368,6 +371,9 @@
     <t>检测到勒索攻击攻击活动—WebShell上传</t>
   </si>
   <si>
+    <t>192.168.100.200</t>
+  </si>
+  <si>
     <t>WebShell上传</t>
   </si>
   <si>
@@ -398,6 +404,9 @@
     <t>检测到银狐攻击攻击活动—DNS隧道</t>
   </si>
   <si>
+    <t>172.17.75.124</t>
+  </si>
+  <si>
     <t>异常行为事件</t>
   </si>
   <si>
@@ -422,6 +431,9 @@
     <t>检测到海莲花APT攻击攻击活动—远程代码执行</t>
   </si>
   <si>
+    <t>168.196.23.21</t>
+  </si>
+  <si>
     <t>远程代码执行</t>
   </si>
   <si>
@@ -449,6 +461,9 @@
     <t>检测到响尾蛇APT攻击攻击活动—蠕虫传播</t>
   </si>
   <si>
+    <t>192.168.24.241</t>
+  </si>
+  <si>
     <t>蠕虫传播</t>
   </si>
   <si>
@@ -503,6 +518,9 @@
     <t>检测到摩诃草APT攻击活动—DNS隧道</t>
   </si>
   <si>
+    <t>192.168.118.232</t>
+  </si>
+  <si>
     <t>摩诃草APT</t>
   </si>
   <si>
@@ -524,7 +542,7 @@
     <t>检测到银狐病毒活动—病毒木马行为</t>
   </si>
   <si>
-    <t>192.168.100.200</t>
+    <t>192.168.254.90</t>
   </si>
   <si>
     <t>病毒木马活动</t>
@@ -545,7 +563,7 @@
     <t>检测到勒索病毒活动—WebShell上传</t>
   </si>
   <si>
-    <t>172.17.75.124</t>
+    <t>10.16.11.65</t>
   </si>
   <si>
     <t>勒索病毒</t>
@@ -566,7 +584,7 @@
     <t>检测到挖矿病毒活动—数据窃取</t>
   </si>
   <si>
-    <t>168.196.23.21</t>
+    <t>10.18.20.115</t>
   </si>
   <si>
     <t>挖矿病毒</t>
@@ -587,7 +605,7 @@
     <t>检测到后门木马活动—文件上传漏洞</t>
   </si>
   <si>
-    <t>192.168.24.241</t>
+    <t>172.20.64.95</t>
   </si>
   <si>
     <t>后门木马</t>
@@ -617,6 +635,9 @@
     <t>检测到下载者木马活动—蠕虫传播</t>
   </si>
   <si>
+    <t>192.168.50.10</t>
+  </si>
+  <si>
     <t>下载者木马</t>
   </si>
   <si>
@@ -635,7 +656,7 @@
     <t>检测到蠕虫病毒活动—CobaltStrike</t>
   </si>
   <si>
-    <t>192.168.118.232</t>
+    <t>10.100.1.50</t>
   </si>
   <si>
     <t>蠕虫病毒</t>
@@ -659,7 +680,7 @@
     <t>检测到银狐病毒活动—数据窃取</t>
   </si>
   <si>
-    <t>192.168.254.90</t>
+    <t>172.16.88.30</t>
   </si>
   <si>
     <t>EDR (343300000000000106),STA (A07D6)</t>
@@ -674,7 +695,7 @@
     <t>检测到勒索病毒活动—系统漏洞攻击</t>
   </si>
   <si>
-    <t>10.16.11.65</t>
+    <t>192.168.1.100</t>
   </si>
   <si>
     <t>系统漏洞攻击</t>
@@ -687,99 +708,6 @@
   </si>
   <si>
     <t>2026-06-03 23:00:00</t>
-  </si>
-  <si>
-    <t>incident-c7957788-18d6-4da3-a6bd-68df798fa694</t>
-  </si>
-  <si>
-    <t>检测到挖矿病毒活动—后门程序</t>
-  </si>
-  <si>
-    <t>10.18.20.115</t>
-  </si>
-  <si>
-    <t>后门程序</t>
-  </si>
-  <si>
-    <t>2026-06-25 00:00:00</t>
-  </si>
-  <si>
-    <t>EDR (343300000000000108),STA (A07D8)</t>
-  </si>
-  <si>
-    <t>lsass.dll（恶意）</t>
-  </si>
-  <si>
-    <t>2026-06-23 23:00:00</t>
-  </si>
-  <si>
-    <t>incident-1c4381dc-4e32-4103-8cef-e815f739fdc3</t>
-  </si>
-  <si>
-    <t>检测到后门木马活动—横向移动</t>
-  </si>
-  <si>
-    <t>172.20.64.95</t>
-  </si>
-  <si>
-    <t>横向移动</t>
-  </si>
-  <si>
-    <t>2026-06-29 00:00:00</t>
-  </si>
-  <si>
-    <t>2026-06-30 00:00:00</t>
-  </si>
-  <si>
-    <t>EDR (343300000000000109),STA (A07D9)</t>
-  </si>
-  <si>
-    <t>security.dll（恶意）</t>
-  </si>
-  <si>
-    <t>2026-06-28 23:00:00</t>
-  </si>
-  <si>
-    <t>incident-4d305f2c-7272-43c2-8fbe-494cb9e5061d</t>
-  </si>
-  <si>
-    <t>检测到下载者木马活动—数据窃取</t>
-  </si>
-  <si>
-    <t>192.168.50.10</t>
-  </si>
-  <si>
-    <t>2026-06-12 00:00:00</t>
-  </si>
-  <si>
-    <t>EDR (343300000000000110),STA (A07DA)</t>
-  </si>
-  <si>
-    <t>kernel32.exe（恶意）</t>
-  </si>
-  <si>
-    <t>2026-06-10 23:00:00</t>
-  </si>
-  <si>
-    <t>incident-dc299149-042b-4c79-93f3-5fb385480412</t>
-  </si>
-  <si>
-    <t>检测到蠕虫病毒活动—命令注入</t>
-  </si>
-  <si>
-    <t>10.100.1.50</t>
-  </si>
-  <si>
-    <t>命令注入</t>
-  </si>
-  <si>
-    <t>EDR (343300000000000111),STA (A07DB)</t>
-  </si>
-  <si>
-    <t>browser.exe（恶意）</t>
-  </si>
-  <si>
-    <t>2026-06-25 23:00:00</t>
   </si>
 </sst>
 </file>
@@ -802,15 +730,15 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -1260,19 +1188,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
@@ -1281,7 +1209,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
@@ -1405,9 +1333,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1726,15 +1656,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:W149"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:W124"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="38.6666666666667" customWidth="1"/>
+    <col min="1" max="1" width="55" customWidth="1"/>
     <col min="3" max="3" width="18.1111111111111" customWidth="1"/>
-    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="5" max="5" width="14.4444444444444" customWidth="1"/>
+    <col min="6" max="6" width="20.1111111111111" customWidth="1"/>
     <col min="9" max="9" width="17.3333333333333" customWidth="1"/>
-    <col min="19" max="19" width="15" customWidth="1"/>
+    <col min="17" max="17" width="11.6666666666667" customWidth="1"/>
+    <col min="19" max="19" width="24.3333333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23">
@@ -1815,7 +1747,7 @@
       <c r="B2" t="s">
         <v>24</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>25</v>
       </c>
       <c r="D2" t="s">
@@ -1824,7 +1756,7 @@
       <c r="E2" t="s">
         <v>27</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="2" t="s">
         <v>28</v>
       </c>
       <c r="G2" t="s">
@@ -1839,7 +1771,7 @@
       <c r="J2" t="s">
         <v>32</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="2" t="s">
         <v>33</v>
       </c>
       <c r="L2" t="s">
@@ -1886,7 +1818,7 @@
       <c r="B3" t="s">
         <v>44</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D3" t="s">
@@ -1957,8 +1889,8 @@
       <c r="B4" t="s">
         <v>60</v>
       </c>
-      <c r="C4" t="s">
-        <v>45</v>
+      <c r="C4" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="D4" t="s">
         <v>26</v>
@@ -1967,22 +1899,22 @@
         <v>27</v>
       </c>
       <c r="F4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I4" t="s">
         <v>49</v>
       </c>
       <c r="J4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K4" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="L4" t="s">
         <v>66</v>
@@ -2028,7 +1960,7 @@
       <c r="B5" t="s">
         <v>75</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="1" t="s">
         <v>76</v>
       </c>
       <c r="D5" t="s">
@@ -2043,7 +1975,7 @@
       <c r="G5" t="s">
         <v>78</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="H5" s="2" t="s">
         <v>79</v>
       </c>
       <c r="I5" t="s">
@@ -2085,7 +2017,7 @@
       <c r="U5" t="s">
         <v>26</v>
       </c>
-      <c r="V5" s="1" t="s">
+      <c r="V5" s="2" t="s">
         <v>88</v>
       </c>
       <c r="W5" t="s">
@@ -2099,7 +2031,7 @@
       <c r="B6" t="s">
         <v>91</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="1" t="s">
         <v>92</v>
       </c>
       <c r="D6" t="s">
@@ -2108,13 +2040,13 @@
       <c r="E6" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="H6" s="2" t="s">
         <v>79</v>
       </c>
       <c r="I6" t="s">
@@ -2124,13 +2056,13 @@
         <v>93</v>
       </c>
       <c r="K6" t="s">
-        <v>33</v>
+        <v>94</v>
       </c>
       <c r="L6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="N6" t="s">
         <v>36</v>
@@ -2142,13 +2074,13 @@
         <v>26</v>
       </c>
       <c r="Q6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="R6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="S6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="T6" t="s">
         <v>26</v>
@@ -2156,22 +2088,22 @@
       <c r="U6" t="s">
         <v>26</v>
       </c>
-      <c r="V6" s="1" t="s">
+      <c r="V6" s="2" t="s">
         <v>88</v>
       </c>
       <c r="W6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:23">
       <c r="A7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B7" t="s">
-        <v>101</v>
-      </c>
-      <c r="C7" t="s">
         <v>102</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>103</v>
       </c>
       <c r="D7" t="s">
         <v>26</v>
@@ -2179,29 +2111,29 @@
       <c r="E7" t="s">
         <v>27</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G7" t="s">
-        <v>47</v>
+      <c r="G7" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="H7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I7" t="s">
         <v>49</v>
       </c>
       <c r="J7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K7" t="s">
         <v>51</v>
       </c>
       <c r="L7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N7" t="s">
         <v>36</v>
@@ -2213,13 +2145,13 @@
         <v>26</v>
       </c>
       <c r="Q7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="R7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="S7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="T7" t="s">
         <v>26</v>
@@ -2231,18 +2163,18 @@
         <v>57</v>
       </c>
       <c r="W7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:23">
       <c r="A8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B8" t="s">
-        <v>111</v>
-      </c>
-      <c r="C8" t="s">
-        <v>45</v>
+        <v>112</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>113</v>
       </c>
       <c r="D8" t="s">
         <v>26</v>
@@ -2254,25 +2186,25 @@
         <v>28</v>
       </c>
       <c r="G8" t="s">
-        <v>62</v>
-      </c>
-      <c r="H8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>79</v>
       </c>
       <c r="I8" t="s">
         <v>49</v>
       </c>
       <c r="J8" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="K8" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="L8" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="M8" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="N8" t="s">
         <v>36</v>
@@ -2284,36 +2216,36 @@
         <v>26</v>
       </c>
       <c r="Q8" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="R8" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="S8" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="T8" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="U8" t="s">
         <v>71</v>
       </c>
-      <c r="V8" s="1" t="s">
+      <c r="V8" s="2" t="s">
         <v>88</v>
       </c>
       <c r="W8" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="9" spans="1:23">
       <c r="A9" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B9" t="s">
-        <v>121</v>
-      </c>
-      <c r="C9" t="s">
-        <v>45</v>
+        <v>123</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>124</v>
       </c>
       <c r="D9" t="s">
         <v>26</v>
@@ -2325,13 +2257,13 @@
         <v>77</v>
       </c>
       <c r="G9" t="s">
-        <v>78</v>
-      </c>
-      <c r="H9" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>79</v>
       </c>
       <c r="I9" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="J9" t="s">
         <v>80</v>
@@ -2340,7 +2272,7 @@
         <v>81</v>
       </c>
       <c r="L9" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="M9" t="s">
         <v>66</v>
@@ -2355,13 +2287,13 @@
         <v>26</v>
       </c>
       <c r="Q9" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="R9" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="S9" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="T9" t="s">
         <v>26</v>
@@ -2369,22 +2301,22 @@
       <c r="U9" t="s">
         <v>71</v>
       </c>
-      <c r="V9" s="1" t="s">
+      <c r="V9" s="2" t="s">
         <v>88</v>
       </c>
       <c r="W9" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="10" ht="8" customHeight="1" spans="1:23">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23">
       <c r="A10" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B10" t="s">
-        <v>129</v>
-      </c>
-      <c r="C10" t="s">
-        <v>45</v>
+        <v>132</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>133</v>
       </c>
       <c r="D10" t="s">
         <v>26</v>
@@ -2392,29 +2324,29 @@
       <c r="E10" t="s">
         <v>27</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F10" s="2" t="s">
         <v>28</v>
       </c>
       <c r="G10" t="s">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="H10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I10" t="s">
         <v>31</v>
       </c>
       <c r="J10" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="K10" t="s">
-        <v>33</v>
+        <v>94</v>
       </c>
       <c r="L10" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="M10" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="N10" t="s">
         <v>36</v>
@@ -2426,13 +2358,13 @@
         <v>26</v>
       </c>
       <c r="Q10" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="R10" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="S10" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="T10" t="s">
         <v>26</v>
@@ -2444,18 +2376,18 @@
         <v>41</v>
       </c>
       <c r="W10" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="11" ht="8" customHeight="1" spans="1:23">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23">
       <c r="A11" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B11" t="s">
-        <v>138</v>
-      </c>
-      <c r="C11" t="s">
-        <v>45</v>
+        <v>142</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>143</v>
       </c>
       <c r="D11" t="s">
         <v>26</v>
@@ -2463,29 +2395,29 @@
       <c r="E11" t="s">
         <v>27</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="F11" s="2" t="s">
         <v>28</v>
       </c>
       <c r="G11" t="s">
-        <v>47</v>
-      </c>
-      <c r="H11" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="H11" s="2" t="s">
         <v>79</v>
       </c>
       <c r="I11" t="s">
         <v>49</v>
       </c>
       <c r="J11" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="K11" t="s">
         <v>51</v>
       </c>
       <c r="L11" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="M11" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="N11" t="s">
         <v>36</v>
@@ -2497,36 +2429,36 @@
         <v>26</v>
       </c>
       <c r="Q11" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="R11" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="S11" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="T11" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="U11" t="s">
         <v>26</v>
       </c>
-      <c r="V11" s="1" t="s">
+      <c r="V11" s="2" t="s">
         <v>88</v>
       </c>
       <c r="W11" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="12" ht="8" customHeight="1" spans="1:23">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23">
       <c r="A12" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="B12" t="s">
-        <v>147</v>
-      </c>
-      <c r="C12" t="s">
-        <v>148</v>
+        <v>152</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>153</v>
       </c>
       <c r="D12" t="s">
         <v>26</v>
@@ -2535,28 +2467,28 @@
         <v>27</v>
       </c>
       <c r="F12" t="s">
-        <v>149</v>
-      </c>
-      <c r="G12" t="s">
-        <v>62</v>
+        <v>154</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="H12" t="s">
         <v>48</v>
       </c>
       <c r="I12" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="J12" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="K12" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="L12" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="M12" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="N12" t="s">
         <v>36</v>
@@ -2568,13 +2500,13 @@
         <v>26</v>
       </c>
       <c r="Q12" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="R12" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="S12" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="T12" t="s">
         <v>26</v>
@@ -2586,18 +2518,18 @@
         <v>72</v>
       </c>
       <c r="W12" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="13" ht="8" customHeight="1" spans="1:23">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23">
       <c r="A13" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="B13" t="s">
-        <v>156</v>
-      </c>
-      <c r="C13" t="s">
-        <v>45</v>
+        <v>161</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>162</v>
       </c>
       <c r="D13" t="s">
         <v>26</v>
@@ -2606,13 +2538,13 @@
         <v>27</v>
       </c>
       <c r="F13" t="s">
-        <v>157</v>
-      </c>
-      <c r="G13" t="s">
+        <v>163</v>
+      </c>
+      <c r="G13" s="2" t="s">
         <v>78</v>
       </c>
       <c r="H13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I13" t="s">
         <v>49</v>
@@ -2624,7 +2556,7 @@
         <v>81</v>
       </c>
       <c r="L13" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="M13" t="s">
         <v>66</v>
@@ -2639,13 +2571,13 @@
         <v>26</v>
       </c>
       <c r="Q13" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="R13" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="S13" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="T13" t="s">
         <v>26</v>
@@ -2654,33 +2586,33 @@
         <v>26</v>
       </c>
       <c r="V13" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="W13" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="14" ht="8" customHeight="1" spans="1:23">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23">
       <c r="A14" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="B14" t="s">
-        <v>163</v>
-      </c>
-      <c r="C14" t="s">
-        <v>164</v>
+        <v>169</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>170</v>
       </c>
       <c r="D14" t="s">
         <v>26</v>
       </c>
       <c r="E14" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="F14" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="G14" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="H14" t="s">
         <v>48</v>
@@ -2689,16 +2621,16 @@
         <v>49</v>
       </c>
       <c r="J14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K14" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="L14" t="s">
         <v>52</v>
       </c>
       <c r="M14" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N14" t="s">
         <v>36</v>
@@ -2713,10 +2645,8 @@
         <v>84</v>
       </c>
       <c r="R14" t="s">
-        <v>167</v>
-      </c>
-      <c r="S14"/>
-      <c r="T14"/>
+        <v>173</v>
+      </c>
       <c r="U14" t="s">
         <v>71</v>
       </c>
@@ -2724,45 +2654,45 @@
         <v>72</v>
       </c>
       <c r="W14" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="15" ht="8" customHeight="1" spans="1:23">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23">
       <c r="A15" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="B15" t="s">
-        <v>170</v>
-      </c>
-      <c r="C15" t="s">
+        <v>176</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="D15" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" t="s">
         <v>171</v>
       </c>
-      <c r="D15" t="s">
-        <v>26</v>
-      </c>
-      <c r="E15" t="s">
-        <v>165</v>
-      </c>
       <c r="F15" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="G15" t="s">
-        <v>62</v>
-      </c>
-      <c r="H15" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H15" s="2" t="s">
         <v>79</v>
       </c>
       <c r="I15" t="s">
         <v>49</v>
       </c>
       <c r="J15" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="K15" t="s">
         <v>81</v>
       </c>
       <c r="L15" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="M15" t="s">
         <v>67</v>
@@ -2780,63 +2710,63 @@
         <v>26</v>
       </c>
       <c r="R15" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="S15" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="T15" t="s">
         <v>26</v>
       </c>
       <c r="U15" t="s">
-        <v>174</v>
-      </c>
-      <c r="V15" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="V15" s="2" t="s">
         <v>88</v>
       </c>
       <c r="W15" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="16" ht="8" customHeight="1" spans="1:23">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23">
       <c r="A16" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="B16" t="s">
-        <v>177</v>
-      </c>
-      <c r="C16" t="s">
-        <v>178</v>
+        <v>183</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>184</v>
       </c>
       <c r="D16" t="s">
         <v>26</v>
       </c>
       <c r="E16" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="F16" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="G16" t="s">
-        <v>78</v>
-      </c>
-      <c r="H16" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H16" s="2" t="s">
         <v>79</v>
       </c>
       <c r="I16" t="s">
         <v>49</v>
       </c>
       <c r="J16" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="K16" t="s">
-        <v>33</v>
+        <v>94</v>
       </c>
       <c r="L16" t="s">
         <v>52</v>
       </c>
       <c r="M16" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N16" t="s">
         <v>36</v>
@@ -2851,7 +2781,7 @@
         <v>26</v>
       </c>
       <c r="R16" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="S16" t="s">
         <v>26</v>
@@ -2860,36 +2790,36 @@
         <v>26</v>
       </c>
       <c r="U16" t="s">
-        <v>182</v>
-      </c>
-      <c r="V16" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="V16" s="2" t="s">
         <v>88</v>
       </c>
       <c r="W16" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="17" ht="8" customHeight="1" spans="1:23">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23">
       <c r="A17" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="B17" t="s">
-        <v>184</v>
-      </c>
-      <c r="C17" t="s">
-        <v>185</v>
+        <v>190</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>191</v>
       </c>
       <c r="D17" t="s">
         <v>26</v>
       </c>
       <c r="E17" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="F17" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="G17" t="s">
-        <v>29</v>
+        <v>78</v>
       </c>
       <c r="H17" t="s">
         <v>48</v>
@@ -2898,16 +2828,16 @@
         <v>31</v>
       </c>
       <c r="J17" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="K17" t="s">
         <v>51</v>
       </c>
       <c r="L17" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="M17" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="N17" t="s">
         <v>36</v>
@@ -2919,10 +2849,10 @@
         <v>26</v>
       </c>
       <c r="Q17" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="R17" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="S17" t="s">
         <v>26</v>
@@ -2931,51 +2861,51 @@
         <v>26</v>
       </c>
       <c r="U17" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="V17" t="s">
         <v>57</v>
       </c>
       <c r="W17" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="18" ht="8" customHeight="1" spans="1:23">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23">
       <c r="A18" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="B18" t="s">
-        <v>194</v>
-      </c>
-      <c r="C18" t="s">
-        <v>148</v>
+        <v>200</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>201</v>
       </c>
       <c r="D18" t="s">
         <v>26</v>
       </c>
       <c r="E18" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="F18" t="s">
-        <v>195</v>
-      </c>
-      <c r="G18" t="s">
-        <v>47</v>
+        <v>202</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="H18" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I18" t="s">
         <v>49</v>
       </c>
       <c r="J18" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="K18" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="L18" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="M18" t="s">
         <v>83</v>
@@ -2993,54 +2923,54 @@
         <v>26</v>
       </c>
       <c r="R18" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="S18" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="T18" t="s">
         <v>87</v>
       </c>
       <c r="U18" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="V18" t="s">
         <v>72</v>
       </c>
       <c r="W18" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="19" ht="8" customHeight="1" spans="1:23">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23">
       <c r="A19" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="B19" t="s">
-        <v>200</v>
-      </c>
-      <c r="C19" t="s">
-        <v>201</v>
+        <v>207</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>208</v>
       </c>
       <c r="D19" t="s">
         <v>26</v>
       </c>
       <c r="E19" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="F19" t="s">
-        <v>202</v>
-      </c>
-      <c r="G19" t="s">
-        <v>62</v>
+        <v>209</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="H19" t="s">
         <v>30</v>
       </c>
       <c r="I19" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="J19" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="K19" t="s">
         <v>81</v>
@@ -3049,7 +2979,7 @@
         <v>35</v>
       </c>
       <c r="M19" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="N19" t="s">
         <v>36</v>
@@ -3064,40 +2994,39 @@
         <v>26</v>
       </c>
       <c r="R19" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="S19" t="s">
-        <v>154</v>
-      </c>
-      <c r="T19"/>
+        <v>159</v>
+      </c>
       <c r="U19" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="V19" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="W19" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="20" ht="8" customHeight="1" spans="1:23">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23">
       <c r="A20" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="B20" t="s">
-        <v>208</v>
-      </c>
-      <c r="C20" t="s">
-        <v>209</v>
+        <v>215</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>216</v>
       </c>
       <c r="D20" t="s">
         <v>26</v>
       </c>
       <c r="E20" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="F20" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="G20" t="s">
         <v>78</v>
@@ -3106,16 +3035,16 @@
         <v>48</v>
       </c>
       <c r="I20" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="J20" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="K20" t="s">
-        <v>33</v>
+        <v>94</v>
       </c>
       <c r="L20" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="M20" t="s">
         <v>67</v>
@@ -3130,10 +3059,10 @@
         <v>26</v>
       </c>
       <c r="Q20" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="R20" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="S20" t="s">
         <v>26</v>
@@ -3142,45 +3071,45 @@
         <v>26</v>
       </c>
       <c r="U20" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="V20" t="s">
         <v>41</v>
       </c>
       <c r="W20" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="21" ht="8" customHeight="1" spans="1:23">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23">
       <c r="A21" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="B21" t="s">
-        <v>213</v>
-      </c>
-      <c r="C21" t="s">
-        <v>214</v>
+        <v>220</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>221</v>
       </c>
       <c r="D21" t="s">
         <v>26</v>
       </c>
       <c r="E21" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="F21" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="G21" t="s">
         <v>29</v>
       </c>
-      <c r="H21" s="1" t="s">
+      <c r="H21" s="2" t="s">
         <v>79</v>
       </c>
       <c r="I21" t="s">
         <v>31</v>
       </c>
       <c r="J21" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="K21" t="s">
         <v>51</v>
@@ -3204,7 +3133,7 @@
         <v>26</v>
       </c>
       <c r="R21" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="S21" t="s">
         <v>26</v>
@@ -3213,295 +3142,19 @@
         <v>26</v>
       </c>
       <c r="U21" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="V21" t="s">
         <v>57</v>
       </c>
       <c r="W21" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="22" ht="8" customHeight="1" spans="1:23">
-      <c r="A22" t="s">
-        <v>219</v>
-      </c>
-      <c r="B22" t="s">
-        <v>220</v>
-      </c>
-      <c r="C22" t="s">
-        <v>221</v>
-      </c>
-      <c r="D22" t="s">
-        <v>26</v>
-      </c>
-      <c r="E22" t="s">
-        <v>165</v>
-      </c>
-      <c r="F22" t="s">
-        <v>179</v>
-      </c>
-      <c r="G22" t="s">
-        <v>47</v>
-      </c>
-      <c r="H22" t="s">
-        <v>30</v>
-      </c>
-      <c r="I22" t="s">
-        <v>150</v>
-      </c>
-      <c r="J22" t="s">
-        <v>222</v>
-      </c>
-      <c r="K22" t="s">
-        <v>65</v>
-      </c>
-      <c r="L22" t="s">
-        <v>113</v>
-      </c>
-      <c r="M22" t="s">
-        <v>223</v>
-      </c>
-      <c r="N22" t="s">
-        <v>36</v>
-      </c>
-      <c r="O22" t="s">
-        <v>26</v>
-      </c>
-      <c r="P22" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>26</v>
-      </c>
-      <c r="R22" t="s">
-        <v>224</v>
-      </c>
-      <c r="S22"/>
-      <c r="T22" t="s">
-        <v>87</v>
-      </c>
-      <c r="U22" t="s">
         <v>225</v>
       </c>
-      <c r="V22" t="s">
-        <v>72</v>
-      </c>
-      <c r="W22" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="23" ht="8" customHeight="1" spans="1:23">
-      <c r="A23" t="s">
-        <v>227</v>
-      </c>
-      <c r="B23" t="s">
-        <v>228</v>
-      </c>
-      <c r="C23" t="s">
-        <v>229</v>
-      </c>
-      <c r="D23" t="s">
-        <v>26</v>
-      </c>
-      <c r="E23" t="s">
-        <v>165</v>
-      </c>
-      <c r="F23" t="s">
-        <v>186</v>
-      </c>
-      <c r="G23" t="s">
-        <v>62</v>
-      </c>
-      <c r="H23" t="s">
-        <v>48</v>
-      </c>
-      <c r="I23" t="s">
-        <v>150</v>
-      </c>
-      <c r="J23" t="s">
-        <v>230</v>
-      </c>
-      <c r="K23" t="s">
-        <v>81</v>
-      </c>
-      <c r="L23" t="s">
-        <v>231</v>
-      </c>
-      <c r="M23" t="s">
-        <v>232</v>
-      </c>
-      <c r="N23" t="s">
-        <v>36</v>
-      </c>
-      <c r="O23" t="s">
-        <v>26</v>
-      </c>
-      <c r="P23" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>37</v>
-      </c>
-      <c r="R23" t="s">
-        <v>233</v>
-      </c>
-      <c r="S23" t="s">
-        <v>26</v>
-      </c>
-      <c r="T23" t="s">
-        <v>26</v>
-      </c>
-      <c r="U23" t="s">
-        <v>234</v>
-      </c>
-      <c r="V23" t="s">
-        <v>161</v>
-      </c>
-      <c r="W23" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="24" ht="8" customHeight="1" spans="1:23">
-      <c r="A24" t="s">
-        <v>236</v>
-      </c>
-      <c r="B24" t="s">
-        <v>237</v>
-      </c>
-      <c r="C24" t="s">
-        <v>238</v>
-      </c>
-      <c r="D24" t="s">
-        <v>26</v>
-      </c>
-      <c r="E24" t="s">
-        <v>165</v>
-      </c>
-      <c r="F24" t="s">
-        <v>195</v>
-      </c>
-      <c r="G24" t="s">
-        <v>78</v>
-      </c>
-      <c r="H24" t="s">
-        <v>63</v>
-      </c>
-      <c r="I24" t="s">
-        <v>122</v>
-      </c>
-      <c r="J24" t="s">
-        <v>180</v>
-      </c>
-      <c r="K24" t="s">
-        <v>33</v>
-      </c>
-      <c r="L24" t="s">
-        <v>94</v>
-      </c>
-      <c r="M24" t="s">
-        <v>239</v>
-      </c>
-      <c r="N24" t="s">
-        <v>36</v>
-      </c>
-      <c r="O24" t="s">
-        <v>26</v>
-      </c>
-      <c r="P24" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>26</v>
-      </c>
-      <c r="R24" t="s">
-        <v>240</v>
-      </c>
-      <c r="S24" t="s">
-        <v>26</v>
-      </c>
-      <c r="T24"/>
-      <c r="U24" t="s">
-        <v>241</v>
-      </c>
-      <c r="V24" t="s">
-        <v>41</v>
-      </c>
-      <c r="W24" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="25" ht="8" customHeight="1" spans="1:23">
-      <c r="A25" t="s">
-        <v>243</v>
-      </c>
-      <c r="B25" t="s">
-        <v>244</v>
-      </c>
-      <c r="C25" t="s">
-        <v>245</v>
-      </c>
-      <c r="D25" t="s">
-        <v>26</v>
-      </c>
-      <c r="E25" t="s">
-        <v>165</v>
-      </c>
-      <c r="F25" t="s">
-        <v>202</v>
-      </c>
-      <c r="G25" t="s">
-        <v>29</v>
-      </c>
-      <c r="H25" t="s">
-        <v>30</v>
-      </c>
-      <c r="I25" t="s">
-        <v>150</v>
-      </c>
-      <c r="J25" t="s">
-        <v>246</v>
-      </c>
-      <c r="K25" t="s">
-        <v>51</v>
-      </c>
-      <c r="L25" t="s">
-        <v>114</v>
-      </c>
-      <c r="M25" t="s">
-        <v>188</v>
-      </c>
-      <c r="N25" t="s">
-        <v>36</v>
-      </c>
-      <c r="O25" t="s">
-        <v>26</v>
-      </c>
-      <c r="P25" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q25" t="s">
-        <v>26</v>
-      </c>
-      <c r="R25" t="s">
-        <v>247</v>
-      </c>
-      <c r="S25" t="s">
-        <v>26</v>
-      </c>
-      <c r="T25" t="s">
-        <v>26</v>
-      </c>
-      <c r="U25" t="s">
-        <v>248</v>
-      </c>
-      <c r="V25" t="s">
-        <v>57</v>
-      </c>
-      <c r="W25" t="s">
-        <v>249</v>
-      </c>
-    </row>
+    </row>
+    <row r="22" hidden="1"/>
+    <row r="23" hidden="1"/>
+    <row r="24" hidden="1"/>
+    <row r="25" hidden="1"/>
     <row r="26" ht="8" customHeight="1"/>
     <row r="27" ht="8" customHeight="1"/>
     <row r="28" ht="8" customHeight="1"/>
@@ -3509,38 +3162,100 @@
     <row r="30" ht="8" customHeight="1"/>
     <row r="31" ht="8" customHeight="1"/>
     <row r="32" ht="8" customHeight="1"/>
-    <row r="33" ht="8" customHeight="1"/>
-    <row r="34" ht="8" customHeight="1"/>
-    <row r="35" ht="8" customHeight="1"/>
-    <row r="36" ht="8" customHeight="1"/>
-    <row r="37" ht="8" customHeight="1"/>
-    <row r="38" ht="8" customHeight="1"/>
-    <row r="39" ht="8" customHeight="1"/>
-    <row r="40" ht="8" customHeight="1"/>
-    <row r="41" ht="8" customHeight="1"/>
-    <row r="42" ht="8" customHeight="1"/>
-    <row r="43" ht="8" customHeight="1"/>
-    <row r="44" ht="8" customHeight="1"/>
-    <row r="45" ht="8" customHeight="1"/>
-    <row r="46" ht="8" customHeight="1"/>
-    <row r="47" ht="8" customHeight="1"/>
-    <row r="48" ht="8" customHeight="1"/>
-    <row r="49" ht="8" customHeight="1"/>
-    <row r="50" ht="8" customHeight="1"/>
-    <row r="51" ht="8" customHeight="1"/>
-    <row r="52" ht="8" customHeight="1"/>
-    <row r="53" ht="8" customHeight="1"/>
-    <row r="54" ht="8" customHeight="1"/>
+    <row r="33" ht="8" customHeight="1" spans="3:3">
+      <c r="C33" s="3"/>
+    </row>
+    <row r="34" ht="8" customHeight="1" spans="3:3">
+      <c r="C34" s="3"/>
+    </row>
+    <row r="35" ht="8" customHeight="1" spans="3:3">
+      <c r="C35" s="3"/>
+    </row>
+    <row r="36" ht="8" customHeight="1" spans="3:3">
+      <c r="C36" s="3"/>
+    </row>
+    <row r="37" ht="8" customHeight="1" spans="3:3">
+      <c r="C37" s="3"/>
+    </row>
+    <row r="38" ht="8" customHeight="1" spans="3:3">
+      <c r="C38" s="3"/>
+    </row>
+    <row r="39" ht="8" customHeight="1" spans="3:3">
+      <c r="C39" s="3"/>
+    </row>
+    <row r="40" ht="8" customHeight="1" spans="3:3">
+      <c r="C40" s="3"/>
+    </row>
+    <row r="41" ht="8" customHeight="1" spans="3:3">
+      <c r="C41" s="3"/>
+    </row>
+    <row r="42" ht="8" customHeight="1" spans="3:3">
+      <c r="C42" s="3"/>
+    </row>
+    <row r="43" ht="8" customHeight="1" spans="3:3">
+      <c r="C43" s="3"/>
+    </row>
+    <row r="44" ht="8" customHeight="1" spans="3:3">
+      <c r="C44" s="3"/>
+    </row>
+    <row r="45" ht="8" customHeight="1" spans="3:3">
+      <c r="C45" s="3"/>
+    </row>
+    <row r="46" ht="8" customHeight="1" spans="3:3">
+      <c r="C46" s="3"/>
+    </row>
+    <row r="47" ht="8" customHeight="1" spans="3:3">
+      <c r="C47" s="3"/>
+    </row>
+    <row r="48" ht="8" customHeight="1" spans="3:3">
+      <c r="C48" s="3"/>
+    </row>
+    <row r="49" ht="8" customHeight="1" spans="3:3">
+      <c r="C49" s="3"/>
+    </row>
+    <row r="50" ht="8" customHeight="1" spans="3:3">
+      <c r="C50" s="3"/>
+    </row>
+    <row r="51" ht="8" customHeight="1" spans="3:3">
+      <c r="C51" s="3"/>
+    </row>
+    <row r="52" ht="8" customHeight="1" spans="3:3">
+      <c r="C52" s="3"/>
+    </row>
+    <row r="53" ht="8" customHeight="1" spans="3:3">
+      <c r="C53" s="3"/>
+    </row>
+    <row r="54" ht="8" customHeight="1" spans="3:3">
+      <c r="C54" s="3"/>
+    </row>
     <row r="55" ht="8" customHeight="1"/>
-    <row r="56" ht="8" customHeight="1"/>
-    <row r="57" ht="8" customHeight="1"/>
-    <row r="58" ht="8" customHeight="1"/>
-    <row r="59" ht="8" customHeight="1"/>
-    <row r="60" ht="8" customHeight="1"/>
-    <row r="61" ht="8" customHeight="1"/>
-    <row r="62" ht="8" customHeight="1"/>
-    <row r="63" ht="8" customHeight="1"/>
-    <row r="64" ht="8" customHeight="1"/>
+    <row r="56" ht="8" customHeight="1" spans="3:3">
+      <c r="C56" s="3"/>
+    </row>
+    <row r="57" ht="8" customHeight="1" spans="3:3">
+      <c r="C57" s="3"/>
+    </row>
+    <row r="58" ht="8" customHeight="1" spans="3:3">
+      <c r="C58" s="3"/>
+    </row>
+    <row r="59" ht="8" customHeight="1" spans="3:3">
+      <c r="C59" s="3"/>
+    </row>
+    <row r="60" ht="8" customHeight="1" spans="3:3">
+      <c r="C60" s="3"/>
+    </row>
+    <row r="61" ht="8" customHeight="1" spans="3:3">
+      <c r="C61" s="3"/>
+    </row>
+    <row r="62" ht="8" customHeight="1" spans="3:3">
+      <c r="C62" s="3"/>
+    </row>
+    <row r="63" ht="8" customHeight="1" spans="3:3">
+      <c r="C63" s="3"/>
+    </row>
+    <row r="64" ht="8" customHeight="1" spans="3:3">
+      <c r="C64" s="3"/>
+    </row>
     <row r="65" ht="8" customHeight="1"/>
     <row r="66" ht="8" customHeight="1"/>
     <row r="67" ht="8" customHeight="1"/>
@@ -3601,33 +3316,14 @@
     <row r="122" ht="8" customHeight="1"/>
     <row r="123" ht="8" customHeight="1"/>
     <row r="124" ht="8" customHeight="1"/>
-    <row r="125" ht="8" customHeight="1"/>
-    <row r="126" ht="8" customHeight="1"/>
-    <row r="127" ht="8" customHeight="1"/>
-    <row r="128" ht="8" customHeight="1"/>
-    <row r="129" ht="8" customHeight="1"/>
-    <row r="130" ht="8" customHeight="1"/>
-    <row r="131" ht="8" customHeight="1"/>
-    <row r="132" ht="8" customHeight="1"/>
-    <row r="133" ht="8" customHeight="1"/>
-    <row r="134" ht="8" customHeight="1"/>
-    <row r="135" ht="8" customHeight="1"/>
-    <row r="136" ht="8" customHeight="1"/>
-    <row r="137" ht="8" customHeight="1"/>
-    <row r="138" ht="8" customHeight="1"/>
-    <row r="139" ht="8" customHeight="1"/>
-    <row r="140" ht="8" customHeight="1"/>
-    <row r="141" ht="8" customHeight="1"/>
-    <row r="142" ht="8" customHeight="1"/>
-    <row r="143" ht="8" customHeight="1"/>
-    <row r="144" ht="8" customHeight="1"/>
-    <row r="145" ht="8" customHeight="1"/>
-    <row r="146" ht="8" customHeight="1"/>
-    <row r="147" ht="8" customHeight="1"/>
-    <row r="148" ht="8" customHeight="1"/>
-    <row r="149" ht="8" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="A1:W57">
+  <autoFilter ref="A1:W25">
+    <filterColumn colId="4">
+      <filters>
+        <filter val="主机失陷活动"/>
+        <filter val="病毒木马活动"/>
+      </filters>
+    </filterColumn>
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tmp/mock_incident_table_v3.xlsx
+++ b/tmp/mock_incident_table_v3.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="8580"/>
+    <workbookView windowWidth="22188" windowHeight="9180"/>
   </bookViews>
   <sheets>
     <sheet name="事件表" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="220">
   <si>
     <t>事件ID</t>
   </si>
@@ -122,7 +122,7 @@
     <t>严重</t>
   </si>
   <si>
-    <t>已忽略</t>
+    <t>处置完成</t>
   </si>
   <si>
     <t>漏洞利用</t>
@@ -173,12 +173,6 @@
     <t>银狐攻击</t>
   </si>
   <si>
-    <t>高危</t>
-  </si>
-  <si>
-    <t>已处理</t>
-  </si>
-  <si>
     <t>恶意程序事件</t>
   </si>
   <si>
@@ -221,12 +215,6 @@
     <t>海莲花APT攻击</t>
   </si>
   <si>
-    <t>中危</t>
-  </si>
-  <si>
-    <t>处理中</t>
-  </si>
-  <si>
     <t>端口扫描</t>
   </si>
   <si>
@@ -264,12 +252,6 @@
   </si>
   <si>
     <t>响尾蛇APT攻击</t>
-  </si>
-  <si>
-    <t>低危</t>
-  </si>
-  <si>
-    <t>处置完成</t>
   </si>
   <si>
     <t>DNS隧道</t>
@@ -1333,11 +1315,10 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1762,7 +1743,7 @@
       <c r="G2" t="s">
         <v>29</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="2" t="s">
         <v>30</v>
       </c>
       <c r="I2" t="s">
@@ -1831,25 +1812,25 @@
         <v>46</v>
       </c>
       <c r="G3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I3" t="s">
         <v>47</v>
       </c>
-      <c r="H3" t="s">
+      <c r="J3" t="s">
         <v>48</v>
       </c>
-      <c r="I3" t="s">
+      <c r="K3" t="s">
         <v>49</v>
       </c>
-      <c r="J3" t="s">
+      <c r="L3" t="s">
         <v>50</v>
       </c>
-      <c r="K3" t="s">
+      <c r="M3" t="s">
         <v>51</v>
-      </c>
-      <c r="L3" t="s">
-        <v>52</v>
-      </c>
-      <c r="M3" t="s">
-        <v>53</v>
       </c>
       <c r="N3" t="s">
         <v>36</v>
@@ -1861,36 +1842,36 @@
         <v>26</v>
       </c>
       <c r="Q3" t="s">
+        <v>52</v>
+      </c>
+      <c r="R3" t="s">
+        <v>53</v>
+      </c>
+      <c r="S3" t="s">
         <v>54</v>
       </c>
-      <c r="R3" t="s">
+      <c r="T3" t="s">
+        <v>26</v>
+      </c>
+      <c r="U3" t="s">
+        <v>26</v>
+      </c>
+      <c r="V3" t="s">
         <v>55</v>
       </c>
-      <c r="S3" t="s">
+      <c r="W3" t="s">
         <v>56</v>
-      </c>
-      <c r="T3" t="s">
-        <v>26</v>
-      </c>
-      <c r="U3" t="s">
-        <v>26</v>
-      </c>
-      <c r="V3" t="s">
-        <v>57</v>
-      </c>
-      <c r="W3" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:23">
       <c r="A4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="B4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>61</v>
       </c>
       <c r="D4" t="s">
         <v>26</v>
@@ -1899,28 +1880,28 @@
         <v>27</v>
       </c>
       <c r="F4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G4" t="s">
-        <v>63</v>
-      </c>
-      <c r="H4" t="s">
-        <v>64</v>
+        <v>29</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="I4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="J4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="K4" t="s">
         <v>33</v>
       </c>
       <c r="L4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="M4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="N4" t="s">
         <v>36</v>
@@ -1932,36 +1913,36 @@
         <v>26</v>
       </c>
       <c r="Q4" t="s">
+        <v>64</v>
+      </c>
+      <c r="R4" t="s">
+        <v>65</v>
+      </c>
+      <c r="S4" t="s">
+        <v>66</v>
+      </c>
+      <c r="T4" t="s">
+        <v>26</v>
+      </c>
+      <c r="U4" t="s">
+        <v>67</v>
+      </c>
+      <c r="V4" t="s">
         <v>68</v>
       </c>
-      <c r="R4" t="s">
+      <c r="W4" t="s">
         <v>69</v>
-      </c>
-      <c r="S4" t="s">
-        <v>70</v>
-      </c>
-      <c r="T4" t="s">
-        <v>26</v>
-      </c>
-      <c r="U4" t="s">
-        <v>71</v>
-      </c>
-      <c r="V4" t="s">
-        <v>72</v>
-      </c>
-      <c r="W4" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:23">
       <c r="A5" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D5" t="s">
         <v>26</v>
@@ -1970,28 +1951,28 @@
         <v>27</v>
       </c>
       <c r="F5" t="s">
+        <v>73</v>
+      </c>
+      <c r="G5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" t="s">
+        <v>47</v>
+      </c>
+      <c r="J5" t="s">
+        <v>74</v>
+      </c>
+      <c r="K5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M5" t="s">
         <v>77</v>
-      </c>
-      <c r="G5" t="s">
-        <v>78</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="I5" t="s">
-        <v>49</v>
-      </c>
-      <c r="J5" t="s">
-        <v>80</v>
-      </c>
-      <c r="K5" t="s">
-        <v>81</v>
-      </c>
-      <c r="L5" t="s">
-        <v>82</v>
-      </c>
-      <c r="M5" t="s">
-        <v>83</v>
       </c>
       <c r="N5" t="s">
         <v>36</v>
@@ -2003,36 +1984,36 @@
         <v>26</v>
       </c>
       <c r="Q5" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="R5" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="S5" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="T5" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="U5" t="s">
         <v>26</v>
       </c>
       <c r="V5" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="W5" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:23">
       <c r="A6" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D6" t="s">
         <v>26</v>
@@ -2043,26 +2024,26 @@
       <c r="F6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" t="s">
         <v>29</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>79</v>
+        <v>30</v>
       </c>
       <c r="I6" t="s">
         <v>31</v>
       </c>
       <c r="J6" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="K6" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="L6" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="M6" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="N6" t="s">
         <v>36</v>
@@ -2074,13 +2055,13 @@
         <v>26</v>
       </c>
       <c r="Q6" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="R6" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="S6" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="T6" t="s">
         <v>26</v>
@@ -2089,21 +2070,21 @@
         <v>26</v>
       </c>
       <c r="V6" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="W6" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" spans="1:23">
       <c r="A7" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B7" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D7" t="s">
         <v>26</v>
@@ -2114,26 +2095,26 @@
       <c r="F7" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G7" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H7" t="s">
-        <v>64</v>
+      <c r="G7" t="s">
+        <v>29</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="I7" t="s">
+        <v>47</v>
+      </c>
+      <c r="J7" t="s">
+        <v>98</v>
+      </c>
+      <c r="K7" t="s">
         <v>49</v>
       </c>
-      <c r="J7" t="s">
-        <v>104</v>
-      </c>
-      <c r="K7" t="s">
-        <v>51</v>
-      </c>
       <c r="L7" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="M7" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="N7" t="s">
         <v>36</v>
@@ -2145,36 +2126,36 @@
         <v>26</v>
       </c>
       <c r="Q7" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="R7" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="S7" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="T7" t="s">
         <v>26</v>
       </c>
       <c r="U7" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="V7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="W7" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8" spans="1:23">
       <c r="A8" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="B8" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="D8" t="s">
         <v>26</v>
@@ -2189,22 +2170,22 @@
         <v>29</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>79</v>
+        <v>30</v>
       </c>
       <c r="I8" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="J8" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="K8" t="s">
         <v>33</v>
       </c>
       <c r="L8" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="M8" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="N8" t="s">
         <v>36</v>
@@ -2216,36 +2197,36 @@
         <v>26</v>
       </c>
       <c r="Q8" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="R8" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="S8" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="T8" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="U8" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="V8" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="W8" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9" spans="1:23">
       <c r="A9" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B9" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="D9" t="s">
         <v>26</v>
@@ -2254,28 +2235,28 @@
         <v>27</v>
       </c>
       <c r="F9" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="G9" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>79</v>
+        <v>30</v>
       </c>
       <c r="I9" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="J9" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="K9" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="L9" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="M9" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="N9" t="s">
         <v>36</v>
@@ -2287,36 +2268,36 @@
         <v>26</v>
       </c>
       <c r="Q9" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="R9" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="S9" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="T9" t="s">
         <v>26</v>
       </c>
       <c r="U9" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="V9" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="W9" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
     </row>
     <row r="10" spans="1:23">
       <c r="A10" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B10" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="D10" t="s">
         <v>26</v>
@@ -2328,25 +2309,25 @@
         <v>28</v>
       </c>
       <c r="G10" t="s">
-        <v>63</v>
-      </c>
-      <c r="H10" t="s">
-        <v>64</v>
+        <v>29</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="I10" t="s">
         <v>31</v>
       </c>
       <c r="J10" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="K10" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="L10" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="M10" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="N10" t="s">
         <v>36</v>
@@ -2358,13 +2339,13 @@
         <v>26</v>
       </c>
       <c r="Q10" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="R10" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="S10" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="T10" t="s">
         <v>26</v>
@@ -2376,18 +2357,18 @@
         <v>41</v>
       </c>
       <c r="W10" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11" spans="1:23">
       <c r="A11" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="B11" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="D11" t="s">
         <v>26</v>
@@ -2399,25 +2380,25 @@
         <v>28</v>
       </c>
       <c r="G11" t="s">
-        <v>78</v>
+        <v>29</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>79</v>
+        <v>30</v>
       </c>
       <c r="I11" t="s">
+        <v>47</v>
+      </c>
+      <c r="J11" t="s">
+        <v>138</v>
+      </c>
+      <c r="K11" t="s">
         <v>49</v>
       </c>
-      <c r="J11" t="s">
-        <v>144</v>
-      </c>
-      <c r="K11" t="s">
-        <v>51</v>
-      </c>
       <c r="L11" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="M11" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="N11" t="s">
         <v>36</v>
@@ -2429,36 +2410,36 @@
         <v>26</v>
       </c>
       <c r="Q11" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="R11" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="S11" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="T11" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="U11" t="s">
         <v>26</v>
       </c>
       <c r="V11" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="W11" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
     </row>
     <row r="12" spans="1:23">
       <c r="A12" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="B12" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="D12" t="s">
         <v>26</v>
@@ -2467,28 +2448,28 @@
         <v>27</v>
       </c>
       <c r="F12" t="s">
-        <v>154</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H12" t="s">
-        <v>48</v>
+        <v>148</v>
+      </c>
+      <c r="G12" t="s">
+        <v>29</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="I12" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="J12" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="K12" t="s">
         <v>33</v>
       </c>
       <c r="L12" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="M12" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="N12" t="s">
         <v>36</v>
@@ -2500,13 +2481,13 @@
         <v>26</v>
       </c>
       <c r="Q12" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="R12" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="S12" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="T12" t="s">
         <v>26</v>
@@ -2515,21 +2496,21 @@
         <v>26</v>
       </c>
       <c r="V12" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="W12" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
     </row>
     <row r="13" spans="1:23">
       <c r="A13" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="B13" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="D13" t="s">
         <v>26</v>
@@ -2538,28 +2519,28 @@
         <v>27</v>
       </c>
       <c r="F13" t="s">
-        <v>163</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H13" t="s">
-        <v>64</v>
+        <v>157</v>
+      </c>
+      <c r="G13" t="s">
+        <v>29</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="I13" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="J13" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="K13" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="L13" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="M13" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="N13" t="s">
         <v>36</v>
@@ -2571,13 +2552,13 @@
         <v>26</v>
       </c>
       <c r="Q13" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="R13" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="S13" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="T13" t="s">
         <v>26</v>
@@ -2586,51 +2567,51 @@
         <v>26</v>
       </c>
       <c r="V13" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="W13" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14" spans="1:23">
       <c r="A14" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="B14" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="D14" t="s">
         <v>26</v>
       </c>
       <c r="E14" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="F14" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="G14" t="s">
         <v>29</v>
       </c>
-      <c r="H14" t="s">
-        <v>48</v>
+      <c r="H14" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="I14" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="J14" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="K14" t="s">
         <v>33</v>
       </c>
       <c r="L14" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="M14" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="N14" t="s">
         <v>36</v>
@@ -2642,60 +2623,60 @@
         <v>26</v>
       </c>
       <c r="Q14" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="R14" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="U14" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="V14" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="W14" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
     </row>
     <row r="15" spans="1:23">
       <c r="A15" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="B15" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="D15" t="s">
         <v>26</v>
       </c>
       <c r="E15" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="F15" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="G15" t="s">
+        <v>29</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I15" t="s">
         <v>47</v>
       </c>
-      <c r="H15" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="I15" t="s">
-        <v>49</v>
-      </c>
       <c r="J15" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="K15" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="L15" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="M15" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="N15" t="s">
         <v>36</v>
@@ -2710,63 +2691,63 @@
         <v>26</v>
       </c>
       <c r="R15" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="S15" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="T15" t="s">
         <v>26</v>
       </c>
       <c r="U15" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="V15" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="W15" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
     </row>
     <row r="16" spans="1:23">
       <c r="A16" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="B16" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="D16" t="s">
         <v>26</v>
       </c>
       <c r="E16" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="F16" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="G16" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>79</v>
+        <v>30</v>
       </c>
       <c r="I16" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="J16" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="K16" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="L16" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="M16" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="N16" t="s">
         <v>36</v>
@@ -2781,7 +2762,7 @@
         <v>26</v>
       </c>
       <c r="R16" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="S16" t="s">
         <v>26</v>
@@ -2790,54 +2771,54 @@
         <v>26</v>
       </c>
       <c r="U16" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="V16" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="W16" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
     </row>
     <row r="17" spans="1:23">
       <c r="A17" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="B17" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="D17" t="s">
         <v>26</v>
       </c>
       <c r="E17" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="F17" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="G17" t="s">
-        <v>78</v>
-      </c>
-      <c r="H17" t="s">
-        <v>48</v>
+        <v>29</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="I17" t="s">
         <v>31</v>
       </c>
       <c r="J17" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="K17" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L17" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="M17" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="N17" t="s">
         <v>36</v>
@@ -2849,10 +2830,10 @@
         <v>26</v>
       </c>
       <c r="Q17" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="R17" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="S17" t="s">
         <v>26</v>
@@ -2861,54 +2842,54 @@
         <v>26</v>
       </c>
       <c r="U17" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="V17" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="W17" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
     </row>
     <row r="18" spans="1:23">
       <c r="A18" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="B18" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="D18" t="s">
         <v>26</v>
       </c>
       <c r="E18" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="F18" t="s">
-        <v>202</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H18" t="s">
-        <v>64</v>
+        <v>196</v>
+      </c>
+      <c r="G18" t="s">
+        <v>29</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="I18" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="J18" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="K18" t="s">
         <v>33</v>
       </c>
       <c r="L18" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="M18" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="N18" t="s">
         <v>36</v>
@@ -2923,63 +2904,63 @@
         <v>26</v>
       </c>
       <c r="R18" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="S18" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="T18" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="U18" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="V18" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="W18" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
     </row>
     <row r="19" spans="1:23">
       <c r="A19" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="B19" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="D19" t="s">
         <v>26</v>
       </c>
       <c r="E19" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="F19" t="s">
-        <v>209</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H19" t="s">
+        <v>203</v>
+      </c>
+      <c r="G19" t="s">
+        <v>29</v>
+      </c>
+      <c r="H19" s="2" t="s">
         <v>30</v>
       </c>
       <c r="I19" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="J19" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="K19" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="L19" t="s">
         <v>35</v>
       </c>
       <c r="M19" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="N19" t="s">
         <v>36</v>
@@ -2994,60 +2975,60 @@
         <v>26</v>
       </c>
       <c r="R19" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="S19" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="U19" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="V19" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="W19" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
     </row>
     <row r="20" spans="1:23">
       <c r="A20" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="B20" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="D20" t="s">
         <v>26</v>
       </c>
       <c r="E20" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="F20" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="G20" t="s">
-        <v>78</v>
-      </c>
-      <c r="H20" t="s">
-        <v>48</v>
+        <v>29</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="I20" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="J20" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="K20" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="L20" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="M20" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="N20" t="s">
         <v>36</v>
@@ -3059,10 +3040,10 @@
         <v>26</v>
       </c>
       <c r="Q20" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="R20" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="S20" t="s">
         <v>26</v>
@@ -3071,54 +3052,54 @@
         <v>26</v>
       </c>
       <c r="U20" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="V20" t="s">
         <v>41</v>
       </c>
       <c r="W20" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
     </row>
     <row r="21" spans="1:23">
       <c r="A21" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="B21" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="D21" t="s">
         <v>26</v>
       </c>
       <c r="E21" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="F21" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="G21" t="s">
         <v>29</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>79</v>
+        <v>30</v>
       </c>
       <c r="I21" t="s">
         <v>31</v>
       </c>
       <c r="J21" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="K21" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L21" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="M21" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="N21" t="s">
         <v>36</v>
@@ -3133,7 +3114,7 @@
         <v>26</v>
       </c>
       <c r="R21" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="S21" t="s">
         <v>26</v>
@@ -3142,13 +3123,13 @@
         <v>26</v>
       </c>
       <c r="U21" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="V21" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="W21" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
     </row>
     <row r="22" hidden="1"/>
@@ -3163,98 +3144,98 @@
     <row r="31" ht="8" customHeight="1"/>
     <row r="32" ht="8" customHeight="1"/>
     <row r="33" ht="8" customHeight="1" spans="3:3">
-      <c r="C33" s="3"/>
+      <c r="C33" s="1"/>
     </row>
     <row r="34" ht="8" customHeight="1" spans="3:3">
-      <c r="C34" s="3"/>
+      <c r="C34" s="1"/>
     </row>
     <row r="35" ht="8" customHeight="1" spans="3:3">
-      <c r="C35" s="3"/>
+      <c r="C35" s="1"/>
     </row>
     <row r="36" ht="8" customHeight="1" spans="3:3">
-      <c r="C36" s="3"/>
+      <c r="C36" s="1"/>
     </row>
     <row r="37" ht="8" customHeight="1" spans="3:3">
-      <c r="C37" s="3"/>
+      <c r="C37" s="1"/>
     </row>
     <row r="38" ht="8" customHeight="1" spans="3:3">
-      <c r="C38" s="3"/>
+      <c r="C38" s="1"/>
     </row>
     <row r="39" ht="8" customHeight="1" spans="3:3">
-      <c r="C39" s="3"/>
+      <c r="C39" s="1"/>
     </row>
     <row r="40" ht="8" customHeight="1" spans="3:3">
-      <c r="C40" s="3"/>
+      <c r="C40" s="1"/>
     </row>
     <row r="41" ht="8" customHeight="1" spans="3:3">
-      <c r="C41" s="3"/>
+      <c r="C41" s="1"/>
     </row>
     <row r="42" ht="8" customHeight="1" spans="3:3">
-      <c r="C42" s="3"/>
+      <c r="C42" s="1"/>
     </row>
     <row r="43" ht="8" customHeight="1" spans="3:3">
-      <c r="C43" s="3"/>
+      <c r="C43" s="1"/>
     </row>
     <row r="44" ht="8" customHeight="1" spans="3:3">
-      <c r="C44" s="3"/>
+      <c r="C44" s="1"/>
     </row>
     <row r="45" ht="8" customHeight="1" spans="3:3">
-      <c r="C45" s="3"/>
+      <c r="C45" s="1"/>
     </row>
     <row r="46" ht="8" customHeight="1" spans="3:3">
-      <c r="C46" s="3"/>
+      <c r="C46" s="1"/>
     </row>
     <row r="47" ht="8" customHeight="1" spans="3:3">
-      <c r="C47" s="3"/>
+      <c r="C47" s="1"/>
     </row>
     <row r="48" ht="8" customHeight="1" spans="3:3">
-      <c r="C48" s="3"/>
+      <c r="C48" s="1"/>
     </row>
     <row r="49" ht="8" customHeight="1" spans="3:3">
-      <c r="C49" s="3"/>
+      <c r="C49" s="1"/>
     </row>
     <row r="50" ht="8" customHeight="1" spans="3:3">
-      <c r="C50" s="3"/>
+      <c r="C50" s="1"/>
     </row>
     <row r="51" ht="8" customHeight="1" spans="3:3">
-      <c r="C51" s="3"/>
+      <c r="C51" s="1"/>
     </row>
     <row r="52" ht="8" customHeight="1" spans="3:3">
-      <c r="C52" s="3"/>
+      <c r="C52" s="1"/>
     </row>
     <row r="53" ht="8" customHeight="1" spans="3:3">
-      <c r="C53" s="3"/>
+      <c r="C53" s="1"/>
     </row>
     <row r="54" ht="8" customHeight="1" spans="3:3">
-      <c r="C54" s="3"/>
+      <c r="C54" s="1"/>
     </row>
     <row r="55" ht="8" customHeight="1"/>
     <row r="56" ht="8" customHeight="1" spans="3:3">
-      <c r="C56" s="3"/>
+      <c r="C56" s="1"/>
     </row>
     <row r="57" ht="8" customHeight="1" spans="3:3">
-      <c r="C57" s="3"/>
+      <c r="C57" s="1"/>
     </row>
     <row r="58" ht="8" customHeight="1" spans="3:3">
-      <c r="C58" s="3"/>
+      <c r="C58" s="1"/>
     </row>
     <row r="59" ht="8" customHeight="1" spans="3:3">
-      <c r="C59" s="3"/>
+      <c r="C59" s="1"/>
     </row>
     <row r="60" ht="8" customHeight="1" spans="3:3">
-      <c r="C60" s="3"/>
+      <c r="C60" s="1"/>
     </row>
     <row r="61" ht="8" customHeight="1" spans="3:3">
-      <c r="C61" s="3"/>
+      <c r="C61" s="1"/>
     </row>
     <row r="62" ht="8" customHeight="1" spans="3:3">
-      <c r="C62" s="3"/>
+      <c r="C62" s="1"/>
     </row>
     <row r="63" ht="8" customHeight="1" spans="3:3">
-      <c r="C63" s="3"/>
+      <c r="C63" s="1"/>
     </row>
     <row r="64" ht="8" customHeight="1" spans="3:3">
-      <c r="C64" s="3"/>
+      <c r="C64" s="1"/>
     </row>
     <row r="65" ht="8" customHeight="1"/>
     <row r="66" ht="8" customHeight="1"/>
@@ -3317,12 +3298,12 @@
     <row r="123" ht="8" customHeight="1"/>
     <row r="124" ht="8" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="A1:W25">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:W25" etc:filterBottomFollowUsedRange="0">
     <filterColumn colId="4">
-      <filters>
-        <filter val="主机失陷活动"/>
-        <filter val="病毒木马活动"/>
-      </filters>
+      <customFilters>
+        <customFilter operator="equal" val="主机失陷活动"/>
+        <customFilter operator="equal" val="病毒木马活动"/>
+      </customFilters>
     </filterColumn>
     <extLst/>
   </autoFilter>

--- a/tmp/mock_incident_table_v3.xlsx
+++ b/tmp/mock_incident_table_v3.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180"/>
+    <workbookView windowWidth="23040" windowHeight="8580"/>
   </bookViews>
   <sheets>
     <sheet name="事件表" sheetId="1" r:id="rId1"/>
@@ -1315,10 +1315,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -3144,98 +3145,98 @@
     <row r="31" ht="8" customHeight="1"/>
     <row r="32" ht="8" customHeight="1"/>
     <row r="33" ht="8" customHeight="1" spans="3:3">
-      <c r="C33" s="1"/>
+      <c r="C33" s="3"/>
     </row>
     <row r="34" ht="8" customHeight="1" spans="3:3">
-      <c r="C34" s="1"/>
+      <c r="C34" s="3"/>
     </row>
     <row r="35" ht="8" customHeight="1" spans="3:3">
-      <c r="C35" s="1"/>
+      <c r="C35" s="3"/>
     </row>
     <row r="36" ht="8" customHeight="1" spans="3:3">
-      <c r="C36" s="1"/>
+      <c r="C36" s="3"/>
     </row>
     <row r="37" ht="8" customHeight="1" spans="3:3">
-      <c r="C37" s="1"/>
+      <c r="C37" s="3"/>
     </row>
     <row r="38" ht="8" customHeight="1" spans="3:3">
-      <c r="C38" s="1"/>
+      <c r="C38" s="3"/>
     </row>
     <row r="39" ht="8" customHeight="1" spans="3:3">
-      <c r="C39" s="1"/>
+      <c r="C39" s="3"/>
     </row>
     <row r="40" ht="8" customHeight="1" spans="3:3">
-      <c r="C40" s="1"/>
+      <c r="C40" s="3"/>
     </row>
     <row r="41" ht="8" customHeight="1" spans="3:3">
-      <c r="C41" s="1"/>
+      <c r="C41" s="3"/>
     </row>
     <row r="42" ht="8" customHeight="1" spans="3:3">
-      <c r="C42" s="1"/>
+      <c r="C42" s="3"/>
     </row>
     <row r="43" ht="8" customHeight="1" spans="3:3">
-      <c r="C43" s="1"/>
+      <c r="C43" s="3"/>
     </row>
     <row r="44" ht="8" customHeight="1" spans="3:3">
-      <c r="C44" s="1"/>
+      <c r="C44" s="3"/>
     </row>
     <row r="45" ht="8" customHeight="1" spans="3:3">
-      <c r="C45" s="1"/>
+      <c r="C45" s="3"/>
     </row>
     <row r="46" ht="8" customHeight="1" spans="3:3">
-      <c r="C46" s="1"/>
+      <c r="C46" s="3"/>
     </row>
     <row r="47" ht="8" customHeight="1" spans="3:3">
-      <c r="C47" s="1"/>
+      <c r="C47" s="3"/>
     </row>
     <row r="48" ht="8" customHeight="1" spans="3:3">
-      <c r="C48" s="1"/>
+      <c r="C48" s="3"/>
     </row>
     <row r="49" ht="8" customHeight="1" spans="3:3">
-      <c r="C49" s="1"/>
+      <c r="C49" s="3"/>
     </row>
     <row r="50" ht="8" customHeight="1" spans="3:3">
-      <c r="C50" s="1"/>
+      <c r="C50" s="3"/>
     </row>
     <row r="51" ht="8" customHeight="1" spans="3:3">
-      <c r="C51" s="1"/>
+      <c r="C51" s="3"/>
     </row>
     <row r="52" ht="8" customHeight="1" spans="3:3">
-      <c r="C52" s="1"/>
+      <c r="C52" s="3"/>
     </row>
     <row r="53" ht="8" customHeight="1" spans="3:3">
-      <c r="C53" s="1"/>
+      <c r="C53" s="3"/>
     </row>
     <row r="54" ht="8" customHeight="1" spans="3:3">
-      <c r="C54" s="1"/>
+      <c r="C54" s="3"/>
     </row>
     <row r="55" ht="8" customHeight="1"/>
     <row r="56" ht="8" customHeight="1" spans="3:3">
-      <c r="C56" s="1"/>
+      <c r="C56" s="3"/>
     </row>
     <row r="57" ht="8" customHeight="1" spans="3:3">
-      <c r="C57" s="1"/>
+      <c r="C57" s="3"/>
     </row>
     <row r="58" ht="8" customHeight="1" spans="3:3">
-      <c r="C58" s="1"/>
+      <c r="C58" s="3"/>
     </row>
     <row r="59" ht="8" customHeight="1" spans="3:3">
-      <c r="C59" s="1"/>
+      <c r="C59" s="3"/>
     </row>
     <row r="60" ht="8" customHeight="1" spans="3:3">
-      <c r="C60" s="1"/>
+      <c r="C60" s="3"/>
     </row>
     <row r="61" ht="8" customHeight="1" spans="3:3">
-      <c r="C61" s="1"/>
+      <c r="C61" s="3"/>
     </row>
     <row r="62" ht="8" customHeight="1" spans="3:3">
-      <c r="C62" s="1"/>
+      <c r="C62" s="3"/>
     </row>
     <row r="63" ht="8" customHeight="1" spans="3:3">
-      <c r="C63" s="1"/>
+      <c r="C63" s="3"/>
     </row>
     <row r="64" ht="8" customHeight="1" spans="3:3">
-      <c r="C64" s="1"/>
+      <c r="C64" s="3"/>
     </row>
     <row r="65" ht="8" customHeight="1"/>
     <row r="66" ht="8" customHeight="1"/>
@@ -3298,12 +3299,12 @@
     <row r="123" ht="8" customHeight="1"/>
     <row r="124" ht="8" customHeight="1"/>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:W25" etc:filterBottomFollowUsedRange="0">
+  <autoFilter ref="A1:W25">
     <filterColumn colId="4">
-      <customFilters>
-        <customFilter operator="equal" val="主机失陷活动"/>
-        <customFilter operator="equal" val="病毒木马活动"/>
-      </customFilters>
+      <filters>
+        <filter val="主机失陷活动"/>
+        <filter val="病毒木马活动"/>
+      </filters>
     </filterColumn>
     <extLst/>
   </autoFilter>

--- a/tmp/mock_incident_table_v3.xlsx
+++ b/tmp/mock_incident_table_v3.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="204">
   <si>
     <t>事件ID</t>
   </si>
@@ -122,10 +122,10 @@
     <t>严重</t>
   </si>
   <si>
-    <t>处置完成</t>
-  </si>
-  <si>
-    <t>漏洞利用</t>
+    <t>处置中</t>
+  </si>
+  <si>
+    <t>恶意程序事件</t>
   </si>
   <si>
     <t>Web应用漏洞</t>
@@ -155,285 +155,258 @@
     <t>evil-c2.xyz（恶意）</t>
   </si>
   <si>
+    <t>已推送</t>
+  </si>
+  <si>
+    <t>2026-06-14 22:00:00</t>
+  </si>
+  <si>
+    <t>incident-ccb79f5b-0c52-45c8-8727-a49ee56da964</t>
+  </si>
+  <si>
+    <t>检测到银狐攻击攻击活动—勒索软件活动</t>
+  </si>
+  <si>
+    <t>银狐攻击</t>
+  </si>
+  <si>
+    <t>吃粽子</t>
+  </si>
+  <si>
+    <t>勒索软件活动</t>
+  </si>
+  <si>
+    <t>攻击</t>
+  </si>
+  <si>
+    <t>2026-06-19 00:00:00</t>
+  </si>
+  <si>
+    <t>2026-06-21 00:00:00</t>
+  </si>
+  <si>
+    <t>103.235.46.91</t>
+  </si>
+  <si>
+    <t>STA (B003E9),EDR (343300000000000002)</t>
+  </si>
+  <si>
+    <t>103.235.46.91（恶意）</t>
+  </si>
+  <si>
+    <t>2026-06-18 22:00:00</t>
+  </si>
+  <si>
+    <t>incident-eaa7bbf6-fade-4c6f-9e52-dc13af32cea8</t>
+  </si>
+  <si>
+    <t>检测到海莲花APT攻击攻击活动—端口扫描</t>
+  </si>
+  <si>
+    <t>海莲花APT攻击</t>
+  </si>
+  <si>
+    <t>端口扫描</t>
+  </si>
+  <si>
+    <t>2026-06-05 00:00:00</t>
+  </si>
+  <si>
+    <t>2026-06-07 00:00:00</t>
+  </si>
+  <si>
+    <t>185.220.101.34</t>
+  </si>
+  <si>
+    <t>STA (B003EA),EDR (343300000000000003)</t>
+  </si>
+  <si>
+    <t>185.220.101.34（恶意）</t>
+  </si>
+  <si>
+    <t>svchost.exe（恶意）</t>
+  </si>
+  <si>
+    <t>2026-06-04 22:00:00</t>
+  </si>
+  <si>
+    <t>incident-beb401e9-92e6-48b6-87a8-5afc3dbe02a2</t>
+  </si>
+  <si>
+    <t>检测到响尾蛇APT攻击攻击活动—DNS隧道</t>
+  </si>
+  <si>
+    <t>响尾蛇APT攻击</t>
+  </si>
+  <si>
+    <t>DNS隧道</t>
+  </si>
+  <si>
+    <t>未成功</t>
+  </si>
+  <si>
+    <t>2026-06-02 00:00:00</t>
+  </si>
+  <si>
+    <t>2026-06-04 00:00:00</t>
+  </si>
+  <si>
+    <t>198.54.117.210</t>
+  </si>
+  <si>
+    <t>STA (B003EB),EDR (343300000000000004)</t>
+  </si>
+  <si>
+    <t>198.54.117.210（恶意）</t>
+  </si>
+  <si>
+    <t>backdoor-gate.net（恶意）</t>
+  </si>
+  <si>
+    <t>2026-06-01 22:00:00</t>
+  </si>
+  <si>
+    <t>incident-b1e6ff99-b2fc-44d0-894c-5c954ffa927e</t>
+  </si>
+  <si>
+    <t>检测到cobaltstrike远控攻击活动—SQL注入漏洞</t>
+  </si>
+  <si>
+    <t>SQL注入漏洞</t>
+  </si>
+  <si>
+    <t>失陷</t>
+  </si>
+  <si>
+    <t>2026-06-11 00:00:00</t>
+  </si>
+  <si>
+    <t>2026-06-13 00:00:00</t>
+  </si>
+  <si>
+    <t>91.121.87.45</t>
+  </si>
+  <si>
+    <t>STA (B003EC),EDR (343300000000000005)</t>
+  </si>
+  <si>
+    <t>91.121.87.45（恶意）</t>
+  </si>
+  <si>
+    <t>2026-06-10 22:00:00</t>
+  </si>
+  <si>
+    <t>incident-5c26e422-343a-4d8d-ab5f-b6e2327a3690</t>
+  </si>
+  <si>
+    <t>检测到摩诃草APT攻击活动—病毒木马行为</t>
+  </si>
+  <si>
+    <t>病毒木马行为</t>
+  </si>
+  <si>
+    <t>2026-06-20 00:00:00</t>
+  </si>
+  <si>
+    <t>2026-06-22 00:00:00</t>
+  </si>
+  <si>
+    <t>23.227.38.65</t>
+  </si>
+  <si>
+    <t>STA (B003ED),EDR (343300000000000006)</t>
+  </si>
+  <si>
+    <t>23.227.38.65（恶意）</t>
+  </si>
+  <si>
+    <t>已遏制</t>
+  </si>
+  <si>
+    <t>2026-06-19 22:00:00</t>
+  </si>
+  <si>
+    <t>incident-f303ded9-35a5-4333-bfc6-8cff61b05333</t>
+  </si>
+  <si>
+    <t>检测到勒索攻击攻击活动—WebShell上传</t>
+  </si>
+  <si>
+    <t>WebShell上传</t>
+  </si>
+  <si>
+    <t>2026-06-24 00:00:00</t>
+  </si>
+  <si>
+    <t>2026-06-26 00:00:00</t>
+  </si>
+  <si>
+    <t>5.188.206.78</t>
+  </si>
+  <si>
+    <t>STA (B003EE),EDR (343300000000000007)</t>
+  </si>
+  <si>
+    <t>5.188.206.78（恶意）</t>
+  </si>
+  <si>
+    <t>ransom-bot.biz（恶意）</t>
+  </si>
+  <si>
+    <t>2026-06-23 22:00:00</t>
+  </si>
+  <si>
+    <t>incident-373a8fbb-9108-49cd-8c81-4e8776da5b6a</t>
+  </si>
+  <si>
+    <t>检测到银狐攻击攻击活动—DNS隧道</t>
+  </si>
+  <si>
+    <t>异常行为事件</t>
+  </si>
+  <si>
+    <t>2026-06-03 00:00:00</t>
+  </si>
+  <si>
+    <t>94.102.61.23</t>
+  </si>
+  <si>
+    <t>STA (B003EF),EDR (343300000000000008)</t>
+  </si>
+  <si>
+    <t>94.102.61.23（恶意）</t>
+  </si>
+  <si>
+    <t>2026-06-02 22:00:00</t>
+  </si>
+  <si>
+    <t>incident-08cddcf6-87ec-4051-91a1-1af581e6e57e</t>
+  </si>
+  <si>
+    <t>检测到海莲花APT攻击攻击活动—远程代码执行</t>
+  </si>
+  <si>
+    <t>远程代码执行</t>
+  </si>
+  <si>
+    <t>2026-06-06 00:00:00</t>
+  </si>
+  <si>
+    <t>2026-06-08 00:00:00</t>
+  </si>
+  <si>
+    <t>185.153.196.30</t>
+  </si>
+  <si>
+    <t>STA (B003F0),EDR (343300000000000009)</t>
+  </si>
+  <si>
+    <t>185.153.196.30（恶意）</t>
+  </si>
+  <si>
     <t>待处理</t>
   </si>
   <si>
-    <t>2026-06-14 22:00:00</t>
-  </si>
-  <si>
-    <t>incident-89635cc4-1b23-44ca-a765-19ccf893c446</t>
-  </si>
-  <si>
-    <t>检测到银狐攻击攻击活动—勒索软件活动</t>
-  </si>
-  <si>
-    <t>192.168.213.156</t>
-  </si>
-  <si>
-    <t>银狐攻击</t>
-  </si>
-  <si>
-    <t>恶意程序事件</t>
-  </si>
-  <si>
-    <t>勒索软件活动</t>
-  </si>
-  <si>
-    <t>攻击</t>
-  </si>
-  <si>
-    <t>2026-06-19 00:00:00</t>
-  </si>
-  <si>
-    <t>2026-06-21 00:00:00</t>
-  </si>
-  <si>
-    <t>103.235.46.91</t>
-  </si>
-  <si>
-    <t>STA (B003E9),EDR (343300000000000002)</t>
-  </si>
-  <si>
-    <t>103.235.46.91（恶意）</t>
-  </si>
-  <si>
-    <t>已遏制</t>
-  </si>
-  <si>
-    <t>2026-06-18 22:00:00</t>
-  </si>
-  <si>
-    <t>incident-eaa7bbf6-fade-4c6f-9e52-dc13af32cea8</t>
-  </si>
-  <si>
-    <t>检测到海莲花APT攻击攻击活动—端口扫描</t>
-  </si>
-  <si>
-    <t>192.168.76.20</t>
-  </si>
-  <si>
-    <t>海莲花APT攻击</t>
-  </si>
-  <si>
-    <t>端口扫描</t>
-  </si>
-  <si>
-    <t>2026-06-05 00:00:00</t>
-  </si>
-  <si>
-    <t>2026-06-07 00:00:00</t>
-  </si>
-  <si>
-    <t>185.220.101.34</t>
-  </si>
-  <si>
-    <t>STA (B003EA),EDR (343300000000000003)</t>
-  </si>
-  <si>
-    <t>185.220.101.34（恶意）</t>
-  </si>
-  <si>
-    <t>svchost.exe（恶意）</t>
-  </si>
-  <si>
-    <t>处置中</t>
-  </si>
-  <si>
-    <t>2026-06-04 22:00:00</t>
-  </si>
-  <si>
-    <t>incident-beb401e9-92e6-48b6-87a8-5afc3dbe02a2</t>
-  </si>
-  <si>
-    <t>检测到响尾蛇APT攻击攻击活动—DNS隧道</t>
-  </si>
-  <si>
-    <t>192.168.200.33</t>
-  </si>
-  <si>
-    <t>响尾蛇APT攻击</t>
-  </si>
-  <si>
-    <t>DNS隧道</t>
-  </si>
-  <si>
-    <t>未成功</t>
-  </si>
-  <si>
-    <t>2026-06-02 00:00:00</t>
-  </si>
-  <si>
-    <t>2026-06-04 00:00:00</t>
-  </si>
-  <si>
-    <t>198.54.117.210</t>
-  </si>
-  <si>
-    <t>STA (B003EB),EDR (343300000000000004)</t>
-  </si>
-  <si>
-    <t>198.54.117.210（恶意）</t>
-  </si>
-  <si>
-    <t>backdoor-gate.net（恶意）</t>
-  </si>
-  <si>
-    <t>已推送</t>
-  </si>
-  <si>
-    <t>2026-06-01 22:00:00</t>
-  </si>
-  <si>
-    <t>incident-b1e6ff99-b2fc-44d0-894c-5c954ffa927e</t>
-  </si>
-  <si>
-    <t>检测到cobaltstrike远控攻击活动—SQL注入漏洞</t>
-  </si>
-  <si>
-    <t>192.168.200.22</t>
-  </si>
-  <si>
-    <t>SQL注入漏洞</t>
-  </si>
-  <si>
-    <t>失陷</t>
-  </si>
-  <si>
-    <t>2026-06-11 00:00:00</t>
-  </si>
-  <si>
-    <t>2026-06-13 00:00:00</t>
-  </si>
-  <si>
-    <t>91.121.87.45</t>
-  </si>
-  <si>
-    <t>STA (B003EC),EDR (343300000000000005)</t>
-  </si>
-  <si>
-    <t>91.121.87.45（恶意）</t>
-  </si>
-  <si>
-    <t>2026-06-10 22:00:00</t>
-  </si>
-  <si>
-    <t>incident-5c26e422-343a-4d8d-ab5f-b6e2327a3690</t>
-  </si>
-  <si>
-    <t>检测到摩诃草APT攻击活动—病毒木马行为</t>
-  </si>
-  <si>
-    <t>192.168.100.205</t>
-  </si>
-  <si>
-    <t>病毒木马行为</t>
-  </si>
-  <si>
-    <t>2026-06-20 00:00:00</t>
-  </si>
-  <si>
-    <t>2026-06-22 00:00:00</t>
-  </si>
-  <si>
-    <t>23.227.38.65</t>
-  </si>
-  <si>
-    <t>STA (B003ED),EDR (343300000000000006)</t>
-  </si>
-  <si>
-    <t>23.227.38.65（恶意）</t>
-  </si>
-  <si>
-    <t>2026-06-19 22:00:00</t>
-  </si>
-  <si>
-    <t>incident-f303ded9-35a5-4333-bfc6-8cff61b05333</t>
-  </si>
-  <si>
-    <t>检测到勒索攻击攻击活动—WebShell上传</t>
-  </si>
-  <si>
-    <t>192.168.100.200</t>
-  </si>
-  <si>
-    <t>WebShell上传</t>
-  </si>
-  <si>
-    <t>2026-06-24 00:00:00</t>
-  </si>
-  <si>
-    <t>2026-06-26 00:00:00</t>
-  </si>
-  <si>
-    <t>5.188.206.78</t>
-  </si>
-  <si>
-    <t>STA (B003EE),EDR (343300000000000007)</t>
-  </si>
-  <si>
-    <t>5.188.206.78（恶意）</t>
-  </si>
-  <si>
-    <t>ransom-bot.biz（恶意）</t>
-  </si>
-  <si>
-    <t>2026-06-23 22:00:00</t>
-  </si>
-  <si>
-    <t>incident-373a8fbb-9108-49cd-8c81-4e8776da5b6a</t>
-  </si>
-  <si>
-    <t>检测到银狐攻击攻击活动—DNS隧道</t>
-  </si>
-  <si>
-    <t>172.17.75.124</t>
-  </si>
-  <si>
-    <t>异常行为事件</t>
-  </si>
-  <si>
-    <t>2026-06-03 00:00:00</t>
-  </si>
-  <si>
-    <t>94.102.61.23</t>
-  </si>
-  <si>
-    <t>STA (B003EF),EDR (343300000000000008)</t>
-  </si>
-  <si>
-    <t>94.102.61.23（恶意）</t>
-  </si>
-  <si>
-    <t>2026-06-02 22:00:00</t>
-  </si>
-  <si>
-    <t>incident-08cddcf6-87ec-4051-91a1-1af581e6e57e</t>
-  </si>
-  <si>
-    <t>检测到海莲花APT攻击攻击活动—远程代码执行</t>
-  </si>
-  <si>
-    <t>168.196.23.21</t>
-  </si>
-  <si>
-    <t>远程代码执行</t>
-  </si>
-  <si>
-    <t>2026-06-06 00:00:00</t>
-  </si>
-  <si>
-    <t>2026-06-08 00:00:00</t>
-  </si>
-  <si>
-    <t>185.153.196.30</t>
-  </si>
-  <si>
-    <t>STA (B003F0),EDR (343300000000000009)</t>
-  </si>
-  <si>
-    <t>185.153.196.30（恶意）</t>
-  </si>
-  <si>
     <t>2026-06-05 22:00:00</t>
   </si>
   <si>
@@ -443,9 +416,6 @@
     <t>检测到响尾蛇APT攻击攻击活动—蠕虫传播</t>
   </si>
   <si>
-    <t>192.168.24.241</t>
-  </si>
-  <si>
     <t>蠕虫传播</t>
   </si>
   <si>
@@ -473,7 +443,7 @@
     <t>检测到cobaltstrike远控攻击活动—CobaltStrike</t>
   </si>
   <si>
-    <t>10.245.224.255</t>
+    <t>病毒木马活动</t>
   </si>
   <si>
     <t>cobaltstrike远控</t>
@@ -500,9 +470,6 @@
     <t>检测到摩诃草APT攻击活动—DNS隧道</t>
   </si>
   <si>
-    <t>192.168.118.232</t>
-  </si>
-  <si>
     <t>摩诃草APT</t>
   </si>
   <si>
@@ -524,12 +491,6 @@
     <t>检测到银狐病毒活动—病毒木马行为</t>
   </si>
   <si>
-    <t>192.168.254.90</t>
-  </si>
-  <si>
-    <t>病毒木马活动</t>
-  </si>
-  <si>
     <t>银狐病毒</t>
   </si>
   <si>
@@ -545,9 +506,6 @@
     <t>检测到勒索病毒活动—WebShell上传</t>
   </si>
   <si>
-    <t>10.16.11.65</t>
-  </si>
-  <si>
     <t>勒索病毒</t>
   </si>
   <si>
@@ -566,9 +524,6 @@
     <t>检测到挖矿病毒活动—数据窃取</t>
   </si>
   <si>
-    <t>10.18.20.115</t>
-  </si>
-  <si>
     <t>挖矿病毒</t>
   </si>
   <si>
@@ -587,9 +542,6 @@
     <t>检测到后门木马活动—文件上传漏洞</t>
   </si>
   <si>
-    <t>172.20.64.95</t>
-  </si>
-  <si>
     <t>后门木马</t>
   </si>
   <si>
@@ -617,9 +569,6 @@
     <t>检测到下载者木马活动—蠕虫传播</t>
   </si>
   <si>
-    <t>192.168.50.10</t>
-  </si>
-  <si>
     <t>下载者木马</t>
   </si>
   <si>
@@ -638,12 +587,15 @@
     <t>检测到蠕虫病毒活动—CobaltStrike</t>
   </si>
   <si>
-    <t>10.100.1.50</t>
+    <t>123活动</t>
   </si>
   <si>
     <t>蠕虫病毒</t>
   </si>
   <si>
+    <t>漏洞利用事件</t>
+  </si>
+  <si>
     <t>2026-06-18 00:00:00</t>
   </si>
   <si>
@@ -662,7 +614,7 @@
     <t>检测到银狐病毒活动—数据窃取</t>
   </si>
   <si>
-    <t>172.16.88.30</t>
+    <t>124活动</t>
   </si>
   <si>
     <t>EDR (343300000000000106),STA (A07D6)</t>
@@ -677,7 +629,7 @@
     <t>检测到勒索病毒活动—系统漏洞攻击</t>
   </si>
   <si>
-    <t>192.168.1.100</t>
+    <t>125活动</t>
   </si>
   <si>
     <t>系统漏洞攻击</t>
@@ -1315,11 +1267,10 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1638,11 +1589,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr filterMode="1"/>
+  <sheetPr/>
   <dimension ref="A1:W124"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="55" customWidth="1"/>
+    <col min="1" max="1" width="42.1111111111111" customWidth="1"/>
+    <col min="2" max="2" width="20.7777777777778" customWidth="1"/>
     <col min="3" max="3" width="18.1111111111111" customWidth="1"/>
     <col min="5" max="5" width="14.4444444444444" customWidth="1"/>
     <col min="6" max="6" width="20.1111111111111" customWidth="1"/>
@@ -1735,7 +1687,7 @@
       <c r="D2" t="s">
         <v>26</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="2" t="s">
         <v>27</v>
       </c>
       <c r="F2" s="2" t="s">
@@ -1786,7 +1738,7 @@
       <c r="U2" t="s">
         <v>26</v>
       </c>
-      <c r="V2" t="s">
+      <c r="V2" s="2" t="s">
         <v>41</v>
       </c>
       <c r="W2" t="s">
@@ -1801,37 +1753,37 @@
         <v>44</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" t="s">
         <v>45</v>
-      </c>
-      <c r="D3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F3" t="s">
-        <v>46</v>
       </c>
       <c r="G3" t="s">
         <v>29</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="I3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J3" t="s">
         <v>47</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>48</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>49</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>50</v>
-      </c>
-      <c r="M3" t="s">
-        <v>51</v>
       </c>
       <c r="N3" t="s">
         <v>36</v>
@@ -1843,45 +1795,45 @@
         <v>26</v>
       </c>
       <c r="Q3" t="s">
+        <v>51</v>
+      </c>
+      <c r="R3" t="s">
         <v>52</v>
       </c>
-      <c r="R3" t="s">
+      <c r="S3" t="s">
         <v>53</v>
       </c>
-      <c r="S3" t="s">
+      <c r="T3" t="s">
+        <v>26</v>
+      </c>
+      <c r="U3" t="s">
+        <v>26</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="W3" t="s">
         <v>54</v>
-      </c>
-      <c r="T3" t="s">
-        <v>26</v>
-      </c>
-      <c r="U3" t="s">
-        <v>26</v>
-      </c>
-      <c r="V3" t="s">
-        <v>55</v>
-      </c>
-      <c r="W3" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:23">
       <c r="A4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" t="s">
         <v>57</v>
-      </c>
-      <c r="B4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" t="s">
-        <v>60</v>
       </c>
       <c r="G4" t="s">
         <v>29</v>
@@ -1890,19 +1842,19 @@
         <v>30</v>
       </c>
       <c r="I4" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="J4" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="K4" t="s">
         <v>33</v>
       </c>
       <c r="L4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="M4" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="N4" t="s">
         <v>36</v>
@@ -1914,45 +1866,45 @@
         <v>26</v>
       </c>
       <c r="Q4" t="s">
+        <v>61</v>
+      </c>
+      <c r="R4" t="s">
+        <v>62</v>
+      </c>
+      <c r="S4" t="s">
+        <v>63</v>
+      </c>
+      <c r="T4" t="s">
+        <v>26</v>
+      </c>
+      <c r="U4" t="s">
         <v>64</v>
       </c>
-      <c r="R4" t="s">
+      <c r="V4" t="s">
+        <v>30</v>
+      </c>
+      <c r="W4" t="s">
         <v>65</v>
-      </c>
-      <c r="S4" t="s">
-        <v>66</v>
-      </c>
-      <c r="T4" t="s">
-        <v>26</v>
-      </c>
-      <c r="U4" t="s">
-        <v>67</v>
-      </c>
-      <c r="V4" t="s">
-        <v>68</v>
-      </c>
-      <c r="W4" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:23">
       <c r="A5" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>72</v>
+        <v>25</v>
       </c>
       <c r="D5" t="s">
         <v>26</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="2" t="s">
         <v>27</v>
       </c>
       <c r="F5" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="G5" t="s">
         <v>29</v>
@@ -1961,19 +1913,19 @@
         <v>30</v>
       </c>
       <c r="I5" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="J5" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="K5" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="L5" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="M5" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="N5" t="s">
         <v>36</v>
@@ -1985,41 +1937,41 @@
         <v>26</v>
       </c>
       <c r="Q5" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="R5" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="S5" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="T5" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="U5" t="s">
         <v>26</v>
       </c>
       <c r="V5" s="2" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="W5" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:23">
       <c r="A6" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B6" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>86</v>
+        <v>25</v>
       </c>
       <c r="D6" t="s">
         <v>26</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="2" t="s">
         <v>27</v>
       </c>
       <c r="F6" s="2" t="s">
@@ -2035,16 +1987,16 @@
         <v>31</v>
       </c>
       <c r="J6" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="K6" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="L6" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="M6" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="N6" t="s">
         <v>36</v>
@@ -2056,13 +2008,13 @@
         <v>26</v>
       </c>
       <c r="Q6" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="R6" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="S6" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="T6" t="s">
         <v>26</v>
@@ -2071,26 +2023,26 @@
         <v>26</v>
       </c>
       <c r="V6" s="2" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="W6" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:23">
       <c r="A7" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="B7" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>97</v>
+        <v>25</v>
       </c>
       <c r="D7" t="s">
         <v>26</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="2" t="s">
         <v>27</v>
       </c>
       <c r="F7" s="2" t="s">
@@ -2103,19 +2055,19 @@
         <v>30</v>
       </c>
       <c r="I7" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="J7" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="K7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L7" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="M7" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="N7" t="s">
         <v>36</v>
@@ -2127,41 +2079,41 @@
         <v>26</v>
       </c>
       <c r="Q7" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="R7" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="S7" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="T7" t="s">
         <v>26</v>
       </c>
       <c r="U7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="V7" t="s">
-        <v>55</v>
+        <v>96</v>
       </c>
       <c r="W7" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8" spans="1:23">
       <c r="A8" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="B8" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>107</v>
+        <v>25</v>
       </c>
       <c r="D8" t="s">
         <v>26</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="2" t="s">
         <v>27</v>
       </c>
       <c r="F8" t="s">
@@ -2174,19 +2126,19 @@
         <v>30</v>
       </c>
       <c r="I8" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="J8" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="K8" t="s">
         <v>33</v>
       </c>
       <c r="L8" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="M8" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="N8" t="s">
         <v>36</v>
@@ -2198,45 +2150,45 @@
         <v>26</v>
       </c>
       <c r="Q8" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="R8" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="S8" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="T8" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="U8" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="V8" s="2" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="W8" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9" spans="1:23">
       <c r="A9" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="B9" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>118</v>
+        <v>25</v>
       </c>
       <c r="D9" t="s">
         <v>26</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="2" t="s">
         <v>27</v>
       </c>
       <c r="F9" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="G9" t="s">
         <v>29</v>
@@ -2245,19 +2197,19 @@
         <v>30</v>
       </c>
       <c r="I9" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="J9" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="K9" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="L9" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="M9" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="N9" t="s">
         <v>36</v>
@@ -2269,41 +2221,41 @@
         <v>26</v>
       </c>
       <c r="Q9" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="R9" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="S9" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="T9" t="s">
         <v>26</v>
       </c>
       <c r="U9" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="V9" s="2" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="W9" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
     </row>
     <row r="10" spans="1:23">
       <c r="A10" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="B10" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>127</v>
+        <v>25</v>
       </c>
       <c r="D10" t="s">
         <v>26</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="2" t="s">
         <v>27</v>
       </c>
       <c r="F10" s="2" t="s">
@@ -2319,16 +2271,16 @@
         <v>31</v>
       </c>
       <c r="J10" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="K10" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="L10" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="M10" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="N10" t="s">
         <v>36</v>
@@ -2340,13 +2292,13 @@
         <v>26</v>
       </c>
       <c r="Q10" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="R10" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="S10" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="T10" t="s">
         <v>26</v>
@@ -2355,26 +2307,26 @@
         <v>26</v>
       </c>
       <c r="V10" t="s">
-        <v>41</v>
+        <v>124</v>
       </c>
       <c r="W10" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11" spans="1:23">
       <c r="A11" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="B11" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>137</v>
+        <v>25</v>
       </c>
       <c r="D11" t="s">
         <v>26</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="2" t="s">
         <v>27</v>
       </c>
       <c r="F11" s="2" t="s">
@@ -2387,19 +2339,19 @@
         <v>30</v>
       </c>
       <c r="I11" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="J11" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="K11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L11" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="M11" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="N11" t="s">
         <v>36</v>
@@ -2411,45 +2363,45 @@
         <v>26</v>
       </c>
       <c r="Q11" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="R11" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="S11" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="T11" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="U11" t="s">
         <v>26</v>
       </c>
       <c r="V11" s="2" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="W11" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12" spans="1:23">
       <c r="A12" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="B12" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>147</v>
+        <v>25</v>
       </c>
       <c r="D12" t="s">
         <v>26</v>
       </c>
-      <c r="E12" t="s">
-        <v>27</v>
+      <c r="E12" s="2" t="s">
+        <v>137</v>
       </c>
       <c r="F12" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="G12" t="s">
         <v>29</v>
@@ -2458,19 +2410,19 @@
         <v>30</v>
       </c>
       <c r="I12" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="J12" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="K12" t="s">
         <v>33</v>
       </c>
       <c r="L12" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="M12" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="N12" t="s">
         <v>36</v>
@@ -2482,13 +2434,13 @@
         <v>26</v>
       </c>
       <c r="Q12" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="R12" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="S12" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="T12" t="s">
         <v>26</v>
@@ -2497,30 +2449,30 @@
         <v>26</v>
       </c>
       <c r="V12" t="s">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="W12" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13" spans="1:23">
       <c r="A13" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="B13" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>156</v>
+        <v>25</v>
       </c>
       <c r="D13" t="s">
         <v>26</v>
       </c>
-      <c r="E13" t="s">
-        <v>27</v>
+      <c r="E13" s="2" t="s">
+        <v>137</v>
       </c>
       <c r="F13" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="G13" t="s">
         <v>29</v>
@@ -2529,19 +2481,19 @@
         <v>30</v>
       </c>
       <c r="I13" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="J13" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="K13" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="L13" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="M13" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="N13" t="s">
         <v>36</v>
@@ -2553,13 +2505,13 @@
         <v>26</v>
       </c>
       <c r="Q13" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="R13" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="S13" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="T13" t="s">
         <v>26</v>
@@ -2568,30 +2520,30 @@
         <v>26</v>
       </c>
       <c r="V13" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="W13" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
     </row>
     <row r="14" spans="1:23">
       <c r="A14" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="B14" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>164</v>
+        <v>25</v>
       </c>
       <c r="D14" t="s">
         <v>26</v>
       </c>
-      <c r="E14" t="s">
-        <v>165</v>
+      <c r="E14" s="2" t="s">
+        <v>137</v>
       </c>
       <c r="F14" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="G14" t="s">
         <v>29</v>
@@ -2600,19 +2552,19 @@
         <v>30</v>
       </c>
       <c r="I14" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="J14" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="K14" t="s">
         <v>33</v>
       </c>
       <c r="L14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M14" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="N14" t="s">
         <v>36</v>
@@ -2624,39 +2576,39 @@
         <v>26</v>
       </c>
       <c r="Q14" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="R14" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
       <c r="U14" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="V14" t="s">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="W14" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
     </row>
     <row r="15" spans="1:23">
       <c r="A15" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="B15" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>171</v>
+        <v>25</v>
       </c>
       <c r="D15" t="s">
         <v>26</v>
       </c>
-      <c r="E15" t="s">
-        <v>165</v>
+      <c r="E15" s="2" t="s">
+        <v>137</v>
       </c>
       <c r="F15" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="G15" t="s">
         <v>29</v>
@@ -2665,19 +2617,19 @@
         <v>30</v>
       </c>
       <c r="I15" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="J15" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="K15" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="L15" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="M15" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="N15" t="s">
         <v>36</v>
@@ -2692,42 +2644,42 @@
         <v>26</v>
       </c>
       <c r="R15" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="S15" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="T15" t="s">
         <v>26</v>
       </c>
       <c r="U15" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="V15" s="2" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="W15" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
     </row>
     <row r="16" spans="1:23">
       <c r="A16" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="B16" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>178</v>
+        <v>25</v>
       </c>
       <c r="D16" t="s">
         <v>26</v>
       </c>
-      <c r="E16" t="s">
-        <v>165</v>
+      <c r="E16" s="2" t="s">
+        <v>137</v>
       </c>
       <c r="F16" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="G16" t="s">
         <v>29</v>
@@ -2736,19 +2688,19 @@
         <v>30</v>
       </c>
       <c r="I16" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="J16" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="K16" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="L16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M16" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="N16" t="s">
         <v>36</v>
@@ -2763,7 +2715,7 @@
         <v>26</v>
       </c>
       <c r="R16" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="S16" t="s">
         <v>26</v>
@@ -2772,33 +2724,33 @@
         <v>26</v>
       </c>
       <c r="U16" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="V16" s="2" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="W16" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
     </row>
     <row r="17" spans="1:23">
       <c r="A17" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="B17" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>185</v>
+        <v>25</v>
       </c>
       <c r="D17" t="s">
         <v>26</v>
       </c>
-      <c r="E17" t="s">
-        <v>165</v>
+      <c r="E17" s="2" t="s">
+        <v>137</v>
       </c>
       <c r="F17" t="s">
-        <v>186</v>
+        <v>170</v>
       </c>
       <c r="G17" t="s">
         <v>29</v>
@@ -2810,16 +2762,16 @@
         <v>31</v>
       </c>
       <c r="J17" t="s">
-        <v>187</v>
+        <v>171</v>
       </c>
       <c r="K17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L17" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="M17" t="s">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="N17" t="s">
         <v>36</v>
@@ -2831,10 +2783,10 @@
         <v>26</v>
       </c>
       <c r="Q17" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="R17" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="S17" t="s">
         <v>26</v>
@@ -2843,33 +2795,33 @@
         <v>26</v>
       </c>
       <c r="U17" t="s">
-        <v>191</v>
+        <v>175</v>
       </c>
       <c r="V17" t="s">
-        <v>55</v>
+        <v>96</v>
       </c>
       <c r="W17" t="s">
-        <v>192</v>
+        <v>176</v>
       </c>
     </row>
     <row r="18" spans="1:23">
       <c r="A18" t="s">
-        <v>193</v>
+        <v>177</v>
       </c>
       <c r="B18" t="s">
-        <v>194</v>
+        <v>178</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>195</v>
+        <v>25</v>
       </c>
       <c r="D18" t="s">
         <v>26</v>
       </c>
-      <c r="E18" t="s">
-        <v>165</v>
+      <c r="E18" s="2" t="s">
+        <v>137</v>
       </c>
       <c r="F18" t="s">
-        <v>196</v>
+        <v>179</v>
       </c>
       <c r="G18" t="s">
         <v>29</v>
@@ -2878,19 +2830,19 @@
         <v>30</v>
       </c>
       <c r="I18" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="J18" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="K18" t="s">
         <v>33</v>
       </c>
       <c r="L18" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="M18" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="N18" t="s">
         <v>36</v>
@@ -2905,42 +2857,42 @@
         <v>26</v>
       </c>
       <c r="R18" t="s">
-        <v>197</v>
+        <v>180</v>
       </c>
       <c r="S18" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="T18" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="U18" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="V18" t="s">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="W18" t="s">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="19" spans="1:23">
       <c r="A19" t="s">
-        <v>200</v>
+        <v>183</v>
       </c>
       <c r="B19" t="s">
-        <v>201</v>
+        <v>184</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>202</v>
+        <v>25</v>
       </c>
       <c r="D19" t="s">
         <v>26</v>
       </c>
-      <c r="E19" t="s">
-        <v>165</v>
+      <c r="E19" s="2" t="s">
+        <v>185</v>
       </c>
       <c r="F19" t="s">
-        <v>203</v>
+        <v>186</v>
       </c>
       <c r="G19" t="s">
         <v>29</v>
@@ -2948,20 +2900,20 @@
       <c r="H19" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="I19" t="s">
-        <v>149</v>
+      <c r="I19" s="2" t="s">
+        <v>187</v>
       </c>
       <c r="J19" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="K19" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="L19" t="s">
         <v>35</v>
       </c>
       <c r="M19" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="N19" t="s">
         <v>36</v>
@@ -2976,39 +2928,39 @@
         <v>26</v>
       </c>
       <c r="R19" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="S19" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="U19" t="s">
-        <v>206</v>
+        <v>190</v>
       </c>
       <c r="V19" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="W19" t="s">
-        <v>207</v>
+        <v>191</v>
       </c>
     </row>
     <row r="20" spans="1:23">
       <c r="A20" t="s">
-        <v>208</v>
+        <v>192</v>
       </c>
       <c r="B20" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>210</v>
+        <v>25</v>
       </c>
       <c r="D20" t="s">
         <v>26</v>
       </c>
-      <c r="E20" t="s">
-        <v>165</v>
+      <c r="E20" s="2" t="s">
+        <v>194</v>
       </c>
       <c r="F20" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="G20" t="s">
         <v>29</v>
@@ -3016,20 +2968,20 @@
       <c r="H20" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="I20" t="s">
-        <v>149</v>
+      <c r="I20" s="2" t="s">
+        <v>187</v>
       </c>
       <c r="J20" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="K20" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="L20" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="M20" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="N20" t="s">
         <v>36</v>
@@ -3041,10 +2993,10 @@
         <v>26</v>
       </c>
       <c r="Q20" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="R20" t="s">
-        <v>211</v>
+        <v>195</v>
       </c>
       <c r="S20" t="s">
         <v>26</v>
@@ -3053,33 +3005,33 @@
         <v>26</v>
       </c>
       <c r="U20" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="V20" t="s">
-        <v>41</v>
+        <v>124</v>
       </c>
       <c r="W20" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
     </row>
     <row r="21" spans="1:23">
       <c r="A21" t="s">
-        <v>213</v>
+        <v>197</v>
       </c>
       <c r="B21" t="s">
-        <v>214</v>
+        <v>198</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>215</v>
+        <v>25</v>
       </c>
       <c r="D21" t="s">
         <v>26</v>
       </c>
-      <c r="E21" t="s">
-        <v>165</v>
+      <c r="E21" s="2" t="s">
+        <v>199</v>
       </c>
       <c r="F21" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="G21" t="s">
         <v>29</v>
@@ -3087,20 +3039,20 @@
       <c r="H21" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="I21" t="s">
-        <v>31</v>
+      <c r="I21" s="2" t="s">
+        <v>187</v>
       </c>
       <c r="J21" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="K21" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L21" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="M21" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="N21" t="s">
         <v>36</v>
@@ -3115,7 +3067,7 @@
         <v>26</v>
       </c>
       <c r="R21" t="s">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="S21" t="s">
         <v>26</v>
@@ -3124,119 +3076,175 @@
         <v>26</v>
       </c>
       <c r="U21" t="s">
-        <v>218</v>
+        <v>202</v>
       </c>
       <c r="V21" t="s">
-        <v>55</v>
+        <v>96</v>
       </c>
       <c r="W21" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="22" hidden="1"/>
-    <row r="23" hidden="1"/>
-    <row r="24" hidden="1"/>
-    <row r="25" hidden="1"/>
-    <row r="26" ht="8" customHeight="1"/>
-    <row r="27" ht="8" customHeight="1"/>
-    <row r="28" ht="8" customHeight="1"/>
-    <row r="29" ht="8" customHeight="1"/>
-    <row r="30" ht="8" customHeight="1"/>
-    <row r="31" ht="8" customHeight="1"/>
-    <row r="32" ht="8" customHeight="1"/>
-    <row r="33" ht="8" customHeight="1" spans="3:3">
-      <c r="C33" s="3"/>
-    </row>
-    <row r="34" ht="8" customHeight="1" spans="3:3">
-      <c r="C34" s="3"/>
-    </row>
-    <row r="35" ht="8" customHeight="1" spans="3:3">
-      <c r="C35" s="3"/>
-    </row>
-    <row r="36" ht="8" customHeight="1" spans="3:3">
-      <c r="C36" s="3"/>
-    </row>
-    <row r="37" ht="8" customHeight="1" spans="3:3">
-      <c r="C37" s="3"/>
-    </row>
-    <row r="38" ht="8" customHeight="1" spans="3:3">
-      <c r="C38" s="3"/>
-    </row>
-    <row r="39" ht="8" customHeight="1" spans="3:3">
-      <c r="C39" s="3"/>
-    </row>
-    <row r="40" ht="8" customHeight="1" spans="3:3">
-      <c r="C40" s="3"/>
-    </row>
-    <row r="41" ht="8" customHeight="1" spans="3:3">
-      <c r="C41" s="3"/>
+        <v>203</v>
+      </c>
+    </row>
+    <row r="22" spans="3:11">
+      <c r="C22" s="1"/>
+      <c r="F22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="K22" s="2"/>
+    </row>
+    <row r="23" spans="3:8">
+      <c r="C23" s="1"/>
+      <c r="H23" s="2"/>
+    </row>
+    <row r="24" spans="3:8">
+      <c r="C24" s="1"/>
+      <c r="H24" s="2"/>
+    </row>
+    <row r="25" spans="3:22">
+      <c r="C25" s="1"/>
+      <c r="H25" s="2"/>
+      <c r="V25" s="2"/>
+    </row>
+    <row r="26" spans="3:22">
+      <c r="C26" s="1"/>
+      <c r="F26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="V26" s="2"/>
+    </row>
+    <row r="27" spans="3:8">
+      <c r="C27" s="1"/>
+      <c r="F27" s="2"/>
+      <c r="H27" s="2"/>
+    </row>
+    <row r="28" spans="3:22">
+      <c r="C28" s="1"/>
+      <c r="H28" s="2"/>
+      <c r="V28" s="2"/>
+    </row>
+    <row r="29" spans="3:22">
+      <c r="C29" s="1"/>
+      <c r="H29" s="2"/>
+      <c r="V29" s="2"/>
+    </row>
+    <row r="30" spans="3:8">
+      <c r="C30" s="1"/>
+      <c r="F30" s="2"/>
+      <c r="H30" s="2"/>
+    </row>
+    <row r="31" spans="3:22">
+      <c r="C31" s="1"/>
+      <c r="F31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="V31" s="2"/>
+    </row>
+    <row r="32" spans="3:8">
+      <c r="C32" s="1"/>
+      <c r="H32" s="2"/>
+    </row>
+    <row r="33" spans="3:8">
+      <c r="C33" s="1"/>
+      <c r="H33" s="2"/>
+    </row>
+    <row r="34" spans="3:8">
+      <c r="C34" s="1"/>
+      <c r="H34" s="2"/>
+    </row>
+    <row r="35" spans="3:22">
+      <c r="C35" s="1"/>
+      <c r="H35" s="2"/>
+      <c r="V35" s="2"/>
+    </row>
+    <row r="36" spans="3:22">
+      <c r="C36" s="1"/>
+      <c r="H36" s="2"/>
+      <c r="V36" s="2"/>
+    </row>
+    <row r="37" spans="3:8">
+      <c r="C37" s="1"/>
+      <c r="H37" s="2"/>
+    </row>
+    <row r="38" spans="3:8">
+      <c r="C38" s="1"/>
+      <c r="H38" s="2"/>
+    </row>
+    <row r="39" spans="3:8">
+      <c r="C39" s="1"/>
+      <c r="H39" s="2"/>
+    </row>
+    <row r="40" spans="3:8">
+      <c r="C40" s="1"/>
+      <c r="H40" s="2"/>
+    </row>
+    <row r="41" spans="3:8">
+      <c r="C41" s="1"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
     </row>
     <row r="42" ht="8" customHeight="1" spans="3:3">
-      <c r="C42" s="3"/>
+      <c r="C42" s="1"/>
     </row>
     <row r="43" ht="8" customHeight="1" spans="3:3">
-      <c r="C43" s="3"/>
+      <c r="C43" s="1"/>
     </row>
     <row r="44" ht="8" customHeight="1" spans="3:3">
-      <c r="C44" s="3"/>
+      <c r="C44" s="1"/>
     </row>
     <row r="45" ht="8" customHeight="1" spans="3:3">
-      <c r="C45" s="3"/>
+      <c r="C45" s="1"/>
     </row>
     <row r="46" ht="8" customHeight="1" spans="3:3">
-      <c r="C46" s="3"/>
+      <c r="C46" s="1"/>
     </row>
     <row r="47" ht="8" customHeight="1" spans="3:3">
-      <c r="C47" s="3"/>
+      <c r="C47" s="1"/>
     </row>
     <row r="48" ht="8" customHeight="1" spans="3:3">
-      <c r="C48" s="3"/>
+      <c r="C48" s="1"/>
     </row>
     <row r="49" ht="8" customHeight="1" spans="3:3">
-      <c r="C49" s="3"/>
+      <c r="C49" s="1"/>
     </row>
     <row r="50" ht="8" customHeight="1" spans="3:3">
-      <c r="C50" s="3"/>
+      <c r="C50" s="1"/>
     </row>
     <row r="51" ht="8" customHeight="1" spans="3:3">
-      <c r="C51" s="3"/>
+      <c r="C51" s="1"/>
     </row>
     <row r="52" ht="8" customHeight="1" spans="3:3">
-      <c r="C52" s="3"/>
+      <c r="C52" s="1"/>
     </row>
     <row r="53" ht="8" customHeight="1" spans="3:3">
-      <c r="C53" s="3"/>
+      <c r="C53" s="1"/>
     </row>
     <row r="54" ht="8" customHeight="1" spans="3:3">
-      <c r="C54" s="3"/>
+      <c r="C54" s="1"/>
     </row>
     <row r="55" ht="8" customHeight="1"/>
     <row r="56" ht="8" customHeight="1" spans="3:3">
-      <c r="C56" s="3"/>
+      <c r="C56" s="1"/>
     </row>
     <row r="57" ht="8" customHeight="1" spans="3:3">
-      <c r="C57" s="3"/>
+      <c r="C57" s="1"/>
     </row>
     <row r="58" ht="8" customHeight="1" spans="3:3">
-      <c r="C58" s="3"/>
+      <c r="C58" s="1"/>
     </row>
     <row r="59" ht="8" customHeight="1" spans="3:3">
-      <c r="C59" s="3"/>
+      <c r="C59" s="1"/>
     </row>
     <row r="60" ht="8" customHeight="1" spans="3:3">
-      <c r="C60" s="3"/>
+      <c r="C60" s="1"/>
     </row>
     <row r="61" ht="8" customHeight="1" spans="3:3">
-      <c r="C61" s="3"/>
+      <c r="C61" s="1"/>
     </row>
     <row r="62" ht="8" customHeight="1" spans="3:3">
-      <c r="C62" s="3"/>
+      <c r="C62" s="1"/>
     </row>
     <row r="63" ht="8" customHeight="1" spans="3:3">
-      <c r="C63" s="3"/>
+      <c r="C63" s="1"/>
     </row>
     <row r="64" ht="8" customHeight="1" spans="3:3">
-      <c r="C64" s="3"/>
+      <c r="C64" s="1"/>
     </row>
     <row r="65" ht="8" customHeight="1"/>
     <row r="66" ht="8" customHeight="1"/>
@@ -3300,12 +3308,6 @@
     <row r="124" ht="8" customHeight="1"/>
   </sheetData>
   <autoFilter ref="A1:W25">
-    <filterColumn colId="4">
-      <filters>
-        <filter val="主机失陷活动"/>
-        <filter val="病毒木马活动"/>
-      </filters>
-    </filterColumn>
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tmp/mock_incident_table_v3.xlsx
+++ b/tmp/mock_incident_table_v3.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="203">
   <si>
     <t>事件ID</t>
   </si>
@@ -168,9 +168,6 @@
   </si>
   <si>
     <t>银狐攻击</t>
-  </si>
-  <si>
-    <t>吃粽子</t>
   </si>
   <si>
     <t>勒索软件活动</t>
@@ -1768,22 +1765,22 @@
         <v>29</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="I3" t="s">
         <v>31</v>
       </c>
       <c r="J3" t="s">
+        <v>46</v>
+      </c>
+      <c r="K3" t="s">
         <v>47</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>48</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>49</v>
-      </c>
-      <c r="M3" t="s">
-        <v>50</v>
       </c>
       <c r="N3" t="s">
         <v>36</v>
@@ -1795,13 +1792,13 @@
         <v>26</v>
       </c>
       <c r="Q3" t="s">
+        <v>50</v>
+      </c>
+      <c r="R3" t="s">
         <v>51</v>
       </c>
-      <c r="R3" t="s">
+      <c r="S3" t="s">
         <v>52</v>
-      </c>
-      <c r="S3" t="s">
-        <v>53</v>
       </c>
       <c r="T3" t="s">
         <v>26</v>
@@ -1813,15 +1810,15 @@
         <v>41</v>
       </c>
       <c r="W3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:23">
       <c r="A4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" t="s">
         <v>55</v>
-      </c>
-      <c r="B4" t="s">
-        <v>56</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>25</v>
@@ -1833,7 +1830,7 @@
         <v>27</v>
       </c>
       <c r="F4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G4" t="s">
         <v>29</v>
@@ -1845,16 +1842,16 @@
         <v>31</v>
       </c>
       <c r="J4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K4" t="s">
         <v>33</v>
       </c>
       <c r="L4" t="s">
+        <v>58</v>
+      </c>
+      <c r="M4" t="s">
         <v>59</v>
-      </c>
-      <c r="M4" t="s">
-        <v>60</v>
       </c>
       <c r="N4" t="s">
         <v>36</v>
@@ -1866,33 +1863,33 @@
         <v>26</v>
       </c>
       <c r="Q4" t="s">
+        <v>60</v>
+      </c>
+      <c r="R4" t="s">
         <v>61</v>
       </c>
-      <c r="R4" t="s">
+      <c r="S4" t="s">
         <v>62</v>
       </c>
-      <c r="S4" t="s">
+      <c r="T4" t="s">
+        <v>26</v>
+      </c>
+      <c r="U4" t="s">
         <v>63</v>
-      </c>
-      <c r="T4" t="s">
-        <v>26</v>
-      </c>
-      <c r="U4" t="s">
-        <v>64</v>
       </c>
       <c r="V4" t="s">
         <v>30</v>
       </c>
       <c r="W4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:23">
       <c r="A5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B5" t="s">
         <v>66</v>
-      </c>
-      <c r="B5" t="s">
-        <v>67</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>25</v>
@@ -1904,7 +1901,7 @@
         <v>27</v>
       </c>
       <c r="F5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G5" t="s">
         <v>29</v>
@@ -1916,16 +1913,16 @@
         <v>31</v>
       </c>
       <c r="J5" t="s">
+        <v>68</v>
+      </c>
+      <c r="K5" t="s">
         <v>69</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
         <v>70</v>
       </c>
-      <c r="L5" t="s">
+      <c r="M5" t="s">
         <v>71</v>
-      </c>
-      <c r="M5" t="s">
-        <v>72</v>
       </c>
       <c r="N5" t="s">
         <v>36</v>
@@ -1937,16 +1934,16 @@
         <v>26</v>
       </c>
       <c r="Q5" t="s">
+        <v>72</v>
+      </c>
+      <c r="R5" t="s">
         <v>73</v>
       </c>
-      <c r="R5" t="s">
+      <c r="S5" t="s">
         <v>74</v>
       </c>
-      <c r="S5" t="s">
+      <c r="T5" t="s">
         <v>75</v>
-      </c>
-      <c r="T5" t="s">
-        <v>76</v>
       </c>
       <c r="U5" t="s">
         <v>26</v>
@@ -1955,15 +1952,15 @@
         <v>41</v>
       </c>
       <c r="W5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:23">
       <c r="A6" t="s">
+        <v>77</v>
+      </c>
+      <c r="B6" t="s">
         <v>78</v>
-      </c>
-      <c r="B6" t="s">
-        <v>79</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>25</v>
@@ -1987,16 +1984,16 @@
         <v>31</v>
       </c>
       <c r="J6" t="s">
+        <v>79</v>
+      </c>
+      <c r="K6" t="s">
         <v>80</v>
       </c>
-      <c r="K6" t="s">
+      <c r="L6" t="s">
         <v>81</v>
       </c>
-      <c r="L6" t="s">
+      <c r="M6" t="s">
         <v>82</v>
-      </c>
-      <c r="M6" t="s">
-        <v>83</v>
       </c>
       <c r="N6" t="s">
         <v>36</v>
@@ -2008,13 +2005,13 @@
         <v>26</v>
       </c>
       <c r="Q6" t="s">
+        <v>83</v>
+      </c>
+      <c r="R6" t="s">
         <v>84</v>
       </c>
-      <c r="R6" t="s">
+      <c r="S6" t="s">
         <v>85</v>
-      </c>
-      <c r="S6" t="s">
-        <v>86</v>
       </c>
       <c r="T6" t="s">
         <v>26</v>
@@ -2026,15 +2023,15 @@
         <v>41</v>
       </c>
       <c r="W6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" spans="1:23">
       <c r="A7" t="s">
+        <v>87</v>
+      </c>
+      <c r="B7" t="s">
         <v>88</v>
-      </c>
-      <c r="B7" t="s">
-        <v>89</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>25</v>
@@ -2058,16 +2055,16 @@
         <v>31</v>
       </c>
       <c r="J7" t="s">
+        <v>89</v>
+      </c>
+      <c r="K7" t="s">
+        <v>47</v>
+      </c>
+      <c r="L7" t="s">
         <v>90</v>
       </c>
-      <c r="K7" t="s">
-        <v>48</v>
-      </c>
-      <c r="L7" t="s">
+      <c r="M7" t="s">
         <v>91</v>
-      </c>
-      <c r="M7" t="s">
-        <v>92</v>
       </c>
       <c r="N7" t="s">
         <v>36</v>
@@ -2079,33 +2076,33 @@
         <v>26</v>
       </c>
       <c r="Q7" t="s">
+        <v>92</v>
+      </c>
+      <c r="R7" t="s">
         <v>93</v>
       </c>
-      <c r="R7" t="s">
+      <c r="S7" t="s">
         <v>94</v>
       </c>
-      <c r="S7" t="s">
+      <c r="T7" t="s">
+        <v>26</v>
+      </c>
+      <c r="U7" t="s">
+        <v>63</v>
+      </c>
+      <c r="V7" t="s">
         <v>95</v>
       </c>
-      <c r="T7" t="s">
-        <v>26</v>
-      </c>
-      <c r="U7" t="s">
-        <v>64</v>
-      </c>
-      <c r="V7" t="s">
+      <c r="W7" t="s">
         <v>96</v>
-      </c>
-      <c r="W7" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="8" spans="1:23">
       <c r="A8" t="s">
+        <v>97</v>
+      </c>
+      <c r="B8" t="s">
         <v>98</v>
-      </c>
-      <c r="B8" t="s">
-        <v>99</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>25</v>
@@ -2129,16 +2126,16 @@
         <v>31</v>
       </c>
       <c r="J8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K8" t="s">
         <v>33</v>
       </c>
       <c r="L8" t="s">
+        <v>100</v>
+      </c>
+      <c r="M8" t="s">
         <v>101</v>
-      </c>
-      <c r="M8" t="s">
-        <v>102</v>
       </c>
       <c r="N8" t="s">
         <v>36</v>
@@ -2150,33 +2147,33 @@
         <v>26</v>
       </c>
       <c r="Q8" t="s">
+        <v>102</v>
+      </c>
+      <c r="R8" t="s">
         <v>103</v>
       </c>
-      <c r="R8" t="s">
+      <c r="S8" t="s">
         <v>104</v>
       </c>
-      <c r="S8" t="s">
+      <c r="T8" t="s">
         <v>105</v>
       </c>
-      <c r="T8" t="s">
-        <v>106</v>
-      </c>
       <c r="U8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="V8" s="2" t="s">
         <v>41</v>
       </c>
       <c r="W8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="9" spans="1:23">
       <c r="A9" t="s">
+        <v>107</v>
+      </c>
+      <c r="B9" t="s">
         <v>108</v>
-      </c>
-      <c r="B9" t="s">
-        <v>109</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>25</v>
@@ -2188,7 +2185,7 @@
         <v>27</v>
       </c>
       <c r="F9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G9" t="s">
         <v>29</v>
@@ -2197,19 +2194,19 @@
         <v>30</v>
       </c>
       <c r="I9" t="s">
+        <v>109</v>
+      </c>
+      <c r="J9" t="s">
+        <v>68</v>
+      </c>
+      <c r="K9" t="s">
+        <v>69</v>
+      </c>
+      <c r="L9" t="s">
         <v>110</v>
       </c>
-      <c r="J9" t="s">
-        <v>69</v>
-      </c>
-      <c r="K9" t="s">
-        <v>70</v>
-      </c>
-      <c r="L9" t="s">
-        <v>111</v>
-      </c>
       <c r="M9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N9" t="s">
         <v>36</v>
@@ -2221,33 +2218,33 @@
         <v>26</v>
       </c>
       <c r="Q9" t="s">
+        <v>111</v>
+      </c>
+      <c r="R9" t="s">
         <v>112</v>
       </c>
-      <c r="R9" t="s">
+      <c r="S9" t="s">
         <v>113</v>
       </c>
-      <c r="S9" t="s">
-        <v>114</v>
-      </c>
       <c r="T9" t="s">
         <v>26</v>
       </c>
       <c r="U9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="V9" s="2" t="s">
         <v>41</v>
       </c>
       <c r="W9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10" spans="1:23">
       <c r="A10" t="s">
+        <v>115</v>
+      </c>
+      <c r="B10" t="s">
         <v>116</v>
-      </c>
-      <c r="B10" t="s">
-        <v>117</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>25</v>
@@ -2271,16 +2268,16 @@
         <v>31</v>
       </c>
       <c r="J10" t="s">
+        <v>117</v>
+      </c>
+      <c r="K10" t="s">
+        <v>80</v>
+      </c>
+      <c r="L10" t="s">
         <v>118</v>
       </c>
-      <c r="K10" t="s">
-        <v>81</v>
-      </c>
-      <c r="L10" t="s">
+      <c r="M10" t="s">
         <v>119</v>
-      </c>
-      <c r="M10" t="s">
-        <v>120</v>
       </c>
       <c r="N10" t="s">
         <v>36</v>
@@ -2292,33 +2289,33 @@
         <v>26</v>
       </c>
       <c r="Q10" t="s">
+        <v>120</v>
+      </c>
+      <c r="R10" t="s">
         <v>121</v>
       </c>
-      <c r="R10" t="s">
+      <c r="S10" t="s">
         <v>122</v>
       </c>
-      <c r="S10" t="s">
+      <c r="T10" t="s">
+        <v>26</v>
+      </c>
+      <c r="U10" t="s">
+        <v>26</v>
+      </c>
+      <c r="V10" t="s">
         <v>123</v>
       </c>
-      <c r="T10" t="s">
-        <v>26</v>
-      </c>
-      <c r="U10" t="s">
-        <v>26</v>
-      </c>
-      <c r="V10" t="s">
+      <c r="W10" t="s">
         <v>124</v>
-      </c>
-      <c r="W10" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="11" spans="1:23">
       <c r="A11" t="s">
+        <v>125</v>
+      </c>
+      <c r="B11" t="s">
         <v>126</v>
-      </c>
-      <c r="B11" t="s">
-        <v>127</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>25</v>
@@ -2342,16 +2339,16 @@
         <v>31</v>
       </c>
       <c r="J11" t="s">
+        <v>127</v>
+      </c>
+      <c r="K11" t="s">
+        <v>47</v>
+      </c>
+      <c r="L11" t="s">
         <v>128</v>
       </c>
-      <c r="K11" t="s">
-        <v>48</v>
-      </c>
-      <c r="L11" t="s">
-        <v>129</v>
-      </c>
       <c r="M11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="N11" t="s">
         <v>36</v>
@@ -2363,16 +2360,16 @@
         <v>26</v>
       </c>
       <c r="Q11" t="s">
+        <v>129</v>
+      </c>
+      <c r="R11" t="s">
         <v>130</v>
       </c>
-      <c r="R11" t="s">
+      <c r="S11" t="s">
         <v>131</v>
       </c>
-      <c r="S11" t="s">
+      <c r="T11" t="s">
         <v>132</v>
-      </c>
-      <c r="T11" t="s">
-        <v>133</v>
       </c>
       <c r="U11" t="s">
         <v>26</v>
@@ -2381,15 +2378,15 @@
         <v>41</v>
       </c>
       <c r="W11" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12" spans="1:23">
       <c r="A12" t="s">
+        <v>134</v>
+      </c>
+      <c r="B12" t="s">
         <v>135</v>
-      </c>
-      <c r="B12" t="s">
-        <v>136</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>25</v>
@@ -2398,10 +2395,10 @@
         <v>26</v>
       </c>
       <c r="E12" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="F12" t="s">
         <v>137</v>
-      </c>
-      <c r="F12" t="s">
-        <v>138</v>
       </c>
       <c r="G12" t="s">
         <v>29</v>
@@ -2410,19 +2407,19 @@
         <v>30</v>
       </c>
       <c r="I12" t="s">
+        <v>138</v>
+      </c>
+      <c r="J12" t="s">
         <v>139</v>
-      </c>
-      <c r="J12" t="s">
-        <v>140</v>
       </c>
       <c r="K12" t="s">
         <v>33</v>
       </c>
       <c r="L12" t="s">
+        <v>118</v>
+      </c>
+      <c r="M12" t="s">
         <v>119</v>
-      </c>
-      <c r="M12" t="s">
-        <v>120</v>
       </c>
       <c r="N12" t="s">
         <v>36</v>
@@ -2434,13 +2431,13 @@
         <v>26</v>
       </c>
       <c r="Q12" t="s">
+        <v>140</v>
+      </c>
+      <c r="R12" t="s">
         <v>141</v>
       </c>
-      <c r="R12" t="s">
+      <c r="S12" t="s">
         <v>142</v>
-      </c>
-      <c r="S12" t="s">
-        <v>143</v>
       </c>
       <c r="T12" t="s">
         <v>26</v>
@@ -2452,15 +2449,15 @@
         <v>30</v>
       </c>
       <c r="W12" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13" spans="1:23">
       <c r="A13" t="s">
+        <v>143</v>
+      </c>
+      <c r="B13" t="s">
         <v>144</v>
-      </c>
-      <c r="B13" t="s">
-        <v>145</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>25</v>
@@ -2469,10 +2466,10 @@
         <v>26</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F13" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G13" t="s">
         <v>29</v>
@@ -2484,16 +2481,16 @@
         <v>31</v>
       </c>
       <c r="J13" t="s">
+        <v>68</v>
+      </c>
+      <c r="K13" t="s">
         <v>69</v>
       </c>
-      <c r="K13" t="s">
-        <v>70</v>
-      </c>
       <c r="L13" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="M13" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N13" t="s">
         <v>36</v>
@@ -2505,33 +2502,33 @@
         <v>26</v>
       </c>
       <c r="Q13" t="s">
+        <v>146</v>
+      </c>
+      <c r="R13" t="s">
         <v>147</v>
       </c>
-      <c r="R13" t="s">
+      <c r="S13" t="s">
         <v>148</v>
       </c>
-      <c r="S13" t="s">
+      <c r="T13" t="s">
+        <v>26</v>
+      </c>
+      <c r="U13" t="s">
+        <v>26</v>
+      </c>
+      <c r="V13" t="s">
         <v>149</v>
       </c>
-      <c r="T13" t="s">
-        <v>26</v>
-      </c>
-      <c r="U13" t="s">
-        <v>26</v>
-      </c>
-      <c r="V13" t="s">
-        <v>150</v>
-      </c>
       <c r="W13" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="14" spans="1:23">
       <c r="A14" t="s">
+        <v>150</v>
+      </c>
+      <c r="B14" t="s">
         <v>151</v>
-      </c>
-      <c r="B14" t="s">
-        <v>152</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>25</v>
@@ -2540,10 +2537,10 @@
         <v>26</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F14" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G14" t="s">
         <v>29</v>
@@ -2555,16 +2552,16 @@
         <v>31</v>
       </c>
       <c r="J14" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K14" t="s">
         <v>33</v>
       </c>
       <c r="L14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="M14" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="N14" t="s">
         <v>36</v>
@@ -2576,27 +2573,27 @@
         <v>26</v>
       </c>
       <c r="Q14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="R14" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="U14" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="V14" t="s">
         <v>30</v>
       </c>
       <c r="W14" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="15" spans="1:23">
       <c r="A15" t="s">
+        <v>155</v>
+      </c>
+      <c r="B15" t="s">
         <v>156</v>
-      </c>
-      <c r="B15" t="s">
-        <v>157</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>25</v>
@@ -2605,10 +2602,10 @@
         <v>26</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F15" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G15" t="s">
         <v>29</v>
@@ -2620,16 +2617,16 @@
         <v>31</v>
       </c>
       <c r="J15" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="N15" t="s">
         <v>36</v>
@@ -2644,30 +2641,30 @@
         <v>26</v>
       </c>
       <c r="R15" t="s">
+        <v>158</v>
+      </c>
+      <c r="S15" t="s">
+        <v>142</v>
+      </c>
+      <c r="T15" t="s">
+        <v>26</v>
+      </c>
+      <c r="U15" t="s">
         <v>159</v>
-      </c>
-      <c r="S15" t="s">
-        <v>143</v>
-      </c>
-      <c r="T15" t="s">
-        <v>26</v>
-      </c>
-      <c r="U15" t="s">
-        <v>160</v>
       </c>
       <c r="V15" s="2" t="s">
         <v>41</v>
       </c>
       <c r="W15" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" spans="1:23">
       <c r="A16" t="s">
+        <v>161</v>
+      </c>
+      <c r="B16" t="s">
         <v>162</v>
-      </c>
-      <c r="B16" t="s">
-        <v>163</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>25</v>
@@ -2676,10 +2673,10 @@
         <v>26</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F16" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G16" t="s">
         <v>29</v>
@@ -2691,16 +2688,16 @@
         <v>31</v>
       </c>
       <c r="J16" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="L16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="M16" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="N16" t="s">
         <v>36</v>
@@ -2715,30 +2712,30 @@
         <v>26</v>
       </c>
       <c r="R16" t="s">
+        <v>165</v>
+      </c>
+      <c r="S16" t="s">
+        <v>26</v>
+      </c>
+      <c r="T16" t="s">
+        <v>26</v>
+      </c>
+      <c r="U16" t="s">
         <v>166</v>
-      </c>
-      <c r="S16" t="s">
-        <v>26</v>
-      </c>
-      <c r="T16" t="s">
-        <v>26</v>
-      </c>
-      <c r="U16" t="s">
-        <v>167</v>
       </c>
       <c r="V16" s="2" t="s">
         <v>41</v>
       </c>
       <c r="W16" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="17" spans="1:23">
       <c r="A17" t="s">
+        <v>167</v>
+      </c>
+      <c r="B17" t="s">
         <v>168</v>
-      </c>
-      <c r="B17" t="s">
-        <v>169</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>25</v>
@@ -2747,10 +2744,10 @@
         <v>26</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F17" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G17" t="s">
         <v>29</v>
@@ -2762,16 +2759,16 @@
         <v>31</v>
       </c>
       <c r="J17" t="s">
+        <v>170</v>
+      </c>
+      <c r="K17" t="s">
+        <v>47</v>
+      </c>
+      <c r="L17" t="s">
         <v>171</v>
       </c>
-      <c r="K17" t="s">
-        <v>48</v>
-      </c>
-      <c r="L17" t="s">
+      <c r="M17" t="s">
         <v>172</v>
-      </c>
-      <c r="M17" t="s">
-        <v>173</v>
       </c>
       <c r="N17" t="s">
         <v>36</v>
@@ -2783,33 +2780,33 @@
         <v>26</v>
       </c>
       <c r="Q17" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="R17" t="s">
+        <v>173</v>
+      </c>
+      <c r="S17" t="s">
+        <v>26</v>
+      </c>
+      <c r="T17" t="s">
+        <v>26</v>
+      </c>
+      <c r="U17" t="s">
         <v>174</v>
       </c>
-      <c r="S17" t="s">
-        <v>26</v>
-      </c>
-      <c r="T17" t="s">
-        <v>26</v>
-      </c>
-      <c r="U17" t="s">
+      <c r="V17" t="s">
+        <v>95</v>
+      </c>
+      <c r="W17" t="s">
         <v>175</v>
-      </c>
-      <c r="V17" t="s">
-        <v>96</v>
-      </c>
-      <c r="W17" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="18" spans="1:23">
       <c r="A18" t="s">
+        <v>176</v>
+      </c>
+      <c r="B18" t="s">
         <v>177</v>
-      </c>
-      <c r="B18" t="s">
-        <v>178</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>25</v>
@@ -2818,10 +2815,10 @@
         <v>26</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F18" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G18" t="s">
         <v>29</v>
@@ -2833,16 +2830,16 @@
         <v>31</v>
       </c>
       <c r="J18" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="K18" t="s">
         <v>33</v>
       </c>
       <c r="L18" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="M18" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="N18" t="s">
         <v>36</v>
@@ -2857,30 +2854,30 @@
         <v>26</v>
       </c>
       <c r="R18" t="s">
+        <v>179</v>
+      </c>
+      <c r="S18" t="s">
+        <v>142</v>
+      </c>
+      <c r="T18" t="s">
+        <v>75</v>
+      </c>
+      <c r="U18" t="s">
         <v>180</v>
-      </c>
-      <c r="S18" t="s">
-        <v>143</v>
-      </c>
-      <c r="T18" t="s">
-        <v>76</v>
-      </c>
-      <c r="U18" t="s">
-        <v>181</v>
       </c>
       <c r="V18" t="s">
         <v>30</v>
       </c>
       <c r="W18" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="19" spans="1:23">
       <c r="A19" t="s">
+        <v>182</v>
+      </c>
+      <c r="B19" t="s">
         <v>183</v>
-      </c>
-      <c r="B19" t="s">
-        <v>184</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>25</v>
@@ -2889,10 +2886,10 @@
         <v>26</v>
       </c>
       <c r="E19" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="F19" t="s">
         <v>185</v>
-      </c>
-      <c r="F19" t="s">
-        <v>186</v>
       </c>
       <c r="G19" t="s">
         <v>29</v>
@@ -2901,19 +2898,19 @@
         <v>30</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="J19" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L19" t="s">
         <v>35</v>
       </c>
       <c r="M19" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="N19" t="s">
         <v>36</v>
@@ -2928,27 +2925,27 @@
         <v>26</v>
       </c>
       <c r="R19" t="s">
+        <v>188</v>
+      </c>
+      <c r="S19" t="s">
+        <v>142</v>
+      </c>
+      <c r="U19" t="s">
         <v>189</v>
       </c>
-      <c r="S19" t="s">
-        <v>143</v>
-      </c>
-      <c r="U19" t="s">
+      <c r="V19" t="s">
+        <v>149</v>
+      </c>
+      <c r="W19" t="s">
         <v>190</v>
-      </c>
-      <c r="V19" t="s">
-        <v>150</v>
-      </c>
-      <c r="W19" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="20" spans="1:23">
       <c r="A20" t="s">
+        <v>191</v>
+      </c>
+      <c r="B20" t="s">
         <v>192</v>
-      </c>
-      <c r="B20" t="s">
-        <v>193</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>25</v>
@@ -2957,10 +2954,10 @@
         <v>26</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F20" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G20" t="s">
         <v>29</v>
@@ -2969,19 +2966,19 @@
         <v>30</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="J20" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K20" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="L20" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M20" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="N20" t="s">
         <v>36</v>
@@ -2993,33 +2990,33 @@
         <v>26</v>
       </c>
       <c r="Q20" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="R20" t="s">
+        <v>194</v>
+      </c>
+      <c r="S20" t="s">
+        <v>26</v>
+      </c>
+      <c r="T20" t="s">
+        <v>26</v>
+      </c>
+      <c r="U20" t="s">
         <v>195</v>
       </c>
-      <c r="S20" t="s">
-        <v>26</v>
-      </c>
-      <c r="T20" t="s">
-        <v>26</v>
-      </c>
-      <c r="U20" t="s">
-        <v>196</v>
-      </c>
       <c r="V20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="W20" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="21" spans="1:23">
       <c r="A21" t="s">
+        <v>196</v>
+      </c>
+      <c r="B21" t="s">
         <v>197</v>
-      </c>
-      <c r="B21" t="s">
-        <v>198</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>25</v>
@@ -3028,10 +3025,10 @@
         <v>26</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F21" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G21" t="s">
         <v>29</v>
@@ -3040,19 +3037,19 @@
         <v>30</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="J21" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="K21" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="L21" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="M21" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N21" t="s">
         <v>36</v>
@@ -3067,22 +3064,22 @@
         <v>26</v>
       </c>
       <c r="R21" t="s">
+        <v>200</v>
+      </c>
+      <c r="S21" t="s">
+        <v>26</v>
+      </c>
+      <c r="T21" t="s">
+        <v>26</v>
+      </c>
+      <c r="U21" t="s">
         <v>201</v>
       </c>
-      <c r="S21" t="s">
-        <v>26</v>
-      </c>
-      <c r="T21" t="s">
-        <v>26</v>
-      </c>
-      <c r="U21" t="s">
+      <c r="V21" t="s">
+        <v>95</v>
+      </c>
+      <c r="W21" t="s">
         <v>202</v>
-      </c>
-      <c r="V21" t="s">
-        <v>96</v>
-      </c>
-      <c r="W21" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="22" spans="3:11">
